--- a/school_2/floors/КП пол СОШ2.xlsx
+++ b/school_2/floors/КП пол СОШ2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" firstSheet="7" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="КП" sheetId="3" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="4.2" sheetId="14" r:id="rId12"/>
     <sheet name="4.3_ост" sheetId="18" r:id="rId13"/>
     <sheet name="7-Кер" sheetId="15" r:id="rId14"/>
+    <sheet name="8.1_орг" sheetId="20" r:id="rId15"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2664" uniqueCount="674">
   <si>
     <t>Номер п/п</t>
   </si>
@@ -1993,6 +1994,95 @@
   <si>
     <t>2 этаж. 
 КР-1</t>
+  </si>
+  <si>
+    <t>Защитные мероприятия по защите пола от повреждений</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этаж.
+Оргалит</t>
+  </si>
+  <si>
+    <t>№ 
+п. п.</t>
+  </si>
+  <si>
+    <t>1.052</t>
+  </si>
+  <si>
+    <t>1.012</t>
+  </si>
+  <si>
+    <t>1.014</t>
+  </si>
+  <si>
+    <t>1.013</t>
+  </si>
+  <si>
+    <t>1.025</t>
+  </si>
+  <si>
+    <t>1.026</t>
+  </si>
+  <si>
+    <t>1.031</t>
+  </si>
+  <si>
+    <t>1.033</t>
+  </si>
+  <si>
+    <t>1.018</t>
+  </si>
+  <si>
+    <t>1.019</t>
+  </si>
+  <si>
+    <t>1.020</t>
+  </si>
+  <si>
+    <t>1.021</t>
+  </si>
+  <si>
+    <t>1.035</t>
+  </si>
+  <si>
+    <t>1.036</t>
+  </si>
+  <si>
+    <t>1.037</t>
+  </si>
+  <si>
+    <t>1.038</t>
+  </si>
+  <si>
+    <t>1.040</t>
+  </si>
+  <si>
+    <t>1.041</t>
+  </si>
+  <si>
+    <t>1.042</t>
+  </si>
+  <si>
+    <t>1.089</t>
+  </si>
+  <si>
+    <t>1.103</t>
+  </si>
+  <si>
+    <t>1.106</t>
+  </si>
+  <si>
+    <t>1.107</t>
+  </si>
+  <si>
+    <t>1.108</t>
+  </si>
+  <si>
+    <t>1.109</t>
+  </si>
+  <si>
+    <t>1.046</t>
   </si>
 </sst>
 </file>
@@ -2535,7 +2625,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2759,6 +2849,9 @@
     <xf numFmtId="167" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2830,6 +2923,9 @@
     </xf>
     <xf numFmtId="165" fontId="27" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12859,7 +12955,7 @@
       <c r="S255" s="10"/>
       <c r="T255" s="10"/>
     </row>
-    <row r="256" spans="1:20" ht="72" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:20" ht="54" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>418</v>
       </c>
@@ -12993,7 +13089,7 @@
       <c r="S259" s="10"/>
       <c r="T259" s="10"/>
     </row>
-    <row r="260" spans="1:20" ht="72" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:20" ht="54" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>425</v>
       </c>
@@ -13199,7 +13295,7 @@
       <c r="S265" s="10"/>
       <c r="T265" s="10"/>
     </row>
-    <row r="266" spans="1:20" ht="72" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:20" ht="54" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>431</v>
       </c>
@@ -13339,7 +13435,7 @@
       <c r="S269" s="10"/>
       <c r="T269" s="10"/>
     </row>
-    <row r="270" spans="1:20" ht="72" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:20" ht="54" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>435</v>
       </c>
@@ -13464,17 +13560,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -13482,18 +13578,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="100" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -13505,18 +13601,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>413</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="112" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="113" t="s">
         <v>644</v>
       </c>
-      <c r="I3" s="103"/>
+      <c r="I3" s="104"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -13529,18 +13625,18 @@
       <c r="A4" s="89">
         <v>2</v>
       </c>
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="108" t="s">
         <v>387</v>
       </c>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="112" t="s">
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="113" t="s">
         <v>643</v>
       </c>
-      <c r="I4" s="103"/>
+      <c r="I4" s="104"/>
       <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
@@ -14039,17 +14135,17 @@
       <c r="K28" s="95"/>
     </row>
     <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="99" t="s">
+      <c r="A31" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B31" s="99"/>
-      <c r="C31" s="99"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="99"/>
-      <c r="I31" s="99"/>
+      <c r="B31" s="100"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="100"/>
       <c r="J31" s="70"/>
       <c r="K31" s="70"/>
     </row>
@@ -14057,18 +14153,18 @@
       <c r="A32" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B32" s="104" t="s">
+      <c r="B32" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="100" t="s">
+      <c r="C32" s="106"/>
+      <c r="D32" s="106"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="106"/>
+      <c r="G32" s="107"/>
+      <c r="H32" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I32" s="101"/>
+      <c r="I32" s="102"/>
       <c r="J32" s="67" t="s">
         <v>5</v>
       </c>
@@ -14080,18 +14176,18 @@
       <c r="A33" s="89">
         <v>1</v>
       </c>
-      <c r="B33" s="107" t="s">
+      <c r="B33" s="108" t="s">
         <v>413</v>
       </c>
-      <c r="C33" s="108"/>
-      <c r="D33" s="108"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="108"/>
-      <c r="G33" s="109"/>
-      <c r="H33" s="112" t="s">
+      <c r="C33" s="109"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="113" t="s">
         <v>632</v>
       </c>
-      <c r="I33" s="103"/>
+      <c r="I33" s="104"/>
       <c r="J33" s="89" t="s">
         <v>20</v>
       </c>
@@ -14104,18 +14200,18 @@
       <c r="A34" s="89">
         <v>2</v>
       </c>
-      <c r="B34" s="107" t="s">
+      <c r="B34" s="108" t="s">
         <v>387</v>
       </c>
-      <c r="C34" s="108"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="108"/>
-      <c r="F34" s="108"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="112" t="s">
+      <c r="C34" s="109"/>
+      <c r="D34" s="109"/>
+      <c r="E34" s="109"/>
+      <c r="F34" s="109"/>
+      <c r="G34" s="110"/>
+      <c r="H34" s="113" t="s">
         <v>633</v>
       </c>
-      <c r="I34" s="103"/>
+      <c r="I34" s="104"/>
       <c r="J34" s="89" t="s">
         <v>20</v>
       </c>
@@ -14704,17 +14800,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -14722,18 +14818,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="100" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -14745,18 +14841,18 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="114" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="115" t="s">
         <v>636</v>
       </c>
-      <c r="I3" s="115"/>
+      <c r="I3" s="116"/>
       <c r="J3" s="79" t="s">
         <v>20</v>
       </c>
@@ -14775,14 +14871,14 @@
       <c r="C4" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="64" t="s">
@@ -14794,14 +14890,14 @@
       <c r="C5" s="64">
         <v>23.5</v>
       </c>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
@@ -14813,14 +14909,14 @@
       <c r="C6" s="54">
         <v>4.8</v>
       </c>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="64" t="s">
@@ -14832,14 +14928,14 @@
       <c r="C7" s="64">
         <v>19.5</v>
       </c>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="54" t="s">
@@ -14851,14 +14947,14 @@
       <c r="C8" s="54">
         <v>10.3</v>
       </c>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64" t="s">
@@ -14870,14 +14966,14 @@
       <c r="C9" s="64">
         <v>5.6</v>
       </c>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
@@ -14889,14 +14985,14 @@
       <c r="C10" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
@@ -14908,14 +15004,14 @@
       <c r="C11" s="64">
         <v>7.6</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="64" t="s">
@@ -14927,14 +15023,14 @@
       <c r="C12" s="64">
         <v>4.7</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="51" t="s">
@@ -14944,14 +15040,14 @@
         <f>SUM(C5:C12)</f>
         <v>84.199999999999989</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -14986,17 +15082,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -15004,18 +15100,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="100" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -15027,18 +15123,18 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="114" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="115" t="s">
         <v>637</v>
       </c>
-      <c r="I3" s="115"/>
+      <c r="I3" s="116"/>
       <c r="J3" s="79" t="s">
         <v>20</v>
       </c>
@@ -15057,14 +15153,14 @@
       <c r="C4" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="64" t="s">
@@ -15076,14 +15172,14 @@
       <c r="C5" s="64">
         <v>4.8</v>
       </c>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
@@ -15095,14 +15191,14 @@
       <c r="C6" s="54">
         <v>23.6</v>
       </c>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="64" t="s">
@@ -15114,14 +15210,14 @@
       <c r="C7" s="64">
         <v>19.600000000000001</v>
       </c>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="54" t="s">
@@ -15133,14 +15229,14 @@
       <c r="C8" s="54">
         <v>10.5</v>
       </c>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64" t="s">
@@ -15152,14 +15248,14 @@
       <c r="C9" s="64">
         <v>5.6</v>
       </c>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
@@ -15171,14 +15267,14 @@
       <c r="C10" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
@@ -15190,14 +15286,14 @@
       <c r="C11" s="64">
         <v>7.6</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
@@ -15209,14 +15305,14 @@
       <c r="C12" s="54">
         <v>4.5</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="51" t="s">
@@ -15226,14 +15322,14 @@
         <f>SUM(C5:C12)</f>
         <v>84.399999999999991</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -15268,17 +15364,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -15286,18 +15382,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="100" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -15309,18 +15405,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="114" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="115" t="s">
         <v>636</v>
       </c>
-      <c r="I3" s="115"/>
+      <c r="I3" s="116"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -15333,18 +15429,18 @@
       <c r="A4" s="89">
         <v>2</v>
       </c>
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="108" t="s">
         <v>175</v>
       </c>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="114" t="s">
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="115" t="s">
         <v>623</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="116"/>
       <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
@@ -15793,17 +15889,17 @@
       <c r="K26" s="95"/>
     </row>
     <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B28" s="99"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="99"/>
-      <c r="G28" s="99"/>
-      <c r="H28" s="99"/>
-      <c r="I28" s="99"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="100"/>
+      <c r="D28" s="100"/>
+      <c r="E28" s="100"/>
+      <c r="F28" s="100"/>
+      <c r="G28" s="100"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="100"/>
       <c r="J28" s="70"/>
       <c r="K28" s="70"/>
     </row>
@@ -15811,18 +15907,18 @@
       <c r="A29" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B29" s="104" t="s">
+      <c r="B29" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="105"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="100" t="s">
+      <c r="C29" s="106"/>
+      <c r="D29" s="106"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="107"/>
+      <c r="H29" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I29" s="101"/>
+      <c r="I29" s="102"/>
       <c r="J29" s="67" t="s">
         <v>5</v>
       </c>
@@ -15834,18 +15930,18 @@
       <c r="A30" s="89">
         <v>1</v>
       </c>
-      <c r="B30" s="107" t="s">
+      <c r="B30" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="108"/>
-      <c r="D30" s="108"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="108"/>
-      <c r="G30" s="109"/>
-      <c r="H30" s="114" t="s">
+      <c r="C30" s="109"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="109"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="115" t="s">
         <v>637</v>
       </c>
-      <c r="I30" s="115"/>
+      <c r="I30" s="116"/>
       <c r="J30" s="89" t="s">
         <v>20</v>
       </c>
@@ -15858,18 +15954,18 @@
       <c r="A31" s="89">
         <v>2</v>
       </c>
-      <c r="B31" s="107" t="s">
+      <c r="B31" s="108" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="108"/>
-      <c r="D31" s="108"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="109"/>
-      <c r="H31" s="114" t="s">
+      <c r="C31" s="109"/>
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="109"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="115" t="s">
         <v>622</v>
       </c>
-      <c r="I31" s="115"/>
+      <c r="I31" s="116"/>
       <c r="J31" s="89" t="s">
         <v>20</v>
       </c>
@@ -16292,14 +16388,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
       <c r="G1" s="70"/>
       <c r="H1" s="70"/>
     </row>
@@ -16307,15 +16403,15 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="119" t="s">
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="120" t="s">
         <v>631</v>
       </c>
-      <c r="F2" s="119"/>
+      <c r="F2" s="120"/>
       <c r="G2" s="67" t="s">
         <v>5</v>
       </c>
@@ -16327,15 +16423,15 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="118" t="s">
+      <c r="B3" s="119" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="120" t="s">
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="121" t="s">
         <v>192</v>
       </c>
-      <c r="F3" s="120"/>
+      <c r="F3" s="121"/>
       <c r="G3" s="79" t="s">
         <v>20</v>
       </c>
@@ -16345,14 +16441,14 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="98"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
     </row>
     <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
@@ -16370,9 +16466,9 @@
       <c r="E5" s="69" t="s">
         <v>641</v>
       </c>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="84" t="s">
@@ -16391,9 +16487,9 @@
         <f>C6*D6</f>
         <v>6.9375</v>
       </c>
-      <c r="F6" s="113"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="113"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="83" t="s">
@@ -16412,9 +16508,9 @@
         <f>C7*D7</f>
         <v>9.84</v>
       </c>
-      <c r="F7" s="113"/>
-      <c r="G7" s="113"/>
-      <c r="H7" s="113"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="114"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="84" t="s">
@@ -16433,9 +16529,9 @@
         <f t="shared" ref="E8:E11" si="0">C8*D8</f>
         <v>1.425</v>
       </c>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="114"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="83" t="s">
@@ -16454,9 +16550,9 @@
         <f t="shared" si="0"/>
         <v>1.395</v>
       </c>
-      <c r="F9" s="113"/>
-      <c r="G9" s="113"/>
-      <c r="H9" s="113"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="114"/>
+      <c r="H9" s="114"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="84" t="s">
@@ -16475,9 +16571,9 @@
         <f t="shared" si="0"/>
         <v>1.5450000000000002</v>
       </c>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="114"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="83" t="s">
@@ -16496,9 +16592,9 @@
         <f t="shared" si="0"/>
         <v>1.38</v>
       </c>
-      <c r="F11" s="113"/>
-      <c r="G11" s="113"/>
-      <c r="H11" s="113"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="114"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="84" t="s">
@@ -16517,14 +16613,14 @@
         <f t="shared" ref="E12" si="1">C12*D12</f>
         <v>1.38</v>
       </c>
-      <c r="F12" s="113"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="113"/>
+      <c r="F12" s="114"/>
+      <c r="G12" s="114"/>
+      <c r="H12" s="114"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="116"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
+      <c r="A13" s="117"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="117"/>
       <c r="D13" t="s">
         <v>642</v>
       </c>
@@ -16532,9 +16628,9 @@
         <f>SUM(E6:E12)</f>
         <v>23.9025</v>
       </c>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -16548,6 +16644,1037 @@
     <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>625</v>
+      </c>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+    </row>
+    <row r="2" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
+        <v>626</v>
+      </c>
+      <c r="B2" s="105" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
+        <v>631</v>
+      </c>
+      <c r="I2" s="102"/>
+      <c r="J2" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="71" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="97">
+        <v>1</v>
+      </c>
+      <c r="B3" s="108" t="s">
+        <v>645</v>
+      </c>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="115" t="s">
+        <v>646</v>
+      </c>
+      <c r="I3" s="122"/>
+      <c r="J3" s="97" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="72">
+        <f>C32+G36+K29</f>
+        <v>1235.2999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="98"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+    </row>
+    <row r="5" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="69" t="s">
+        <v>647</v>
+      </c>
+      <c r="B5" s="69" t="s">
+        <v>627</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>629</v>
+      </c>
+      <c r="D5" s="99"/>
+      <c r="E5" s="69" t="s">
+        <v>647</v>
+      </c>
+      <c r="F5" s="69" t="s">
+        <v>627</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>629</v>
+      </c>
+      <c r="H5" s="99"/>
+      <c r="I5" s="69" t="s">
+        <v>647</v>
+      </c>
+      <c r="J5" s="69" t="s">
+        <v>627</v>
+      </c>
+      <c r="K5" s="69" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="64">
+        <v>1</v>
+      </c>
+      <c r="B6" s="64" t="s">
+        <v>648</v>
+      </c>
+      <c r="C6" s="64">
+        <v>25.1</v>
+      </c>
+      <c r="D6" s="99"/>
+      <c r="E6" s="64">
+        <v>27</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>560</v>
+      </c>
+      <c r="G6" s="64">
+        <v>13.4</v>
+      </c>
+      <c r="H6" s="99"/>
+      <c r="I6" s="64">
+        <v>57</v>
+      </c>
+      <c r="J6" s="64" t="s">
+        <v>572</v>
+      </c>
+      <c r="K6" s="64">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="54">
+        <v>2</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>649</v>
+      </c>
+      <c r="C7" s="54">
+        <v>12.5</v>
+      </c>
+      <c r="D7" s="99"/>
+      <c r="E7" s="54">
+        <v>28</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>561</v>
+      </c>
+      <c r="G7" s="54">
+        <v>10.26</v>
+      </c>
+      <c r="H7" s="99"/>
+      <c r="I7" s="54">
+        <v>58</v>
+      </c>
+      <c r="J7" s="54" t="s">
+        <v>573</v>
+      </c>
+      <c r="K7" s="54">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="64">
+        <v>3</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>650</v>
+      </c>
+      <c r="C8" s="64">
+        <v>5.4</v>
+      </c>
+      <c r="D8" s="99"/>
+      <c r="E8" s="64">
+        <v>29</v>
+      </c>
+      <c r="F8" s="64" t="s">
+        <v>521</v>
+      </c>
+      <c r="G8" s="64">
+        <v>23.4</v>
+      </c>
+      <c r="H8" s="99"/>
+      <c r="I8" s="64">
+        <v>59</v>
+      </c>
+      <c r="J8" s="64" t="s">
+        <v>540</v>
+      </c>
+      <c r="K8" s="64">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="54">
+        <v>4</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>651</v>
+      </c>
+      <c r="C9" s="54">
+        <v>21</v>
+      </c>
+      <c r="D9" s="99"/>
+      <c r="E9" s="54">
+        <v>30</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>522</v>
+      </c>
+      <c r="G9" s="54">
+        <v>4.67</v>
+      </c>
+      <c r="H9" s="99"/>
+      <c r="I9" s="54">
+        <v>60</v>
+      </c>
+      <c r="J9" s="54" t="s">
+        <v>541</v>
+      </c>
+      <c r="K9" s="54">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="64">
+        <v>5</v>
+      </c>
+      <c r="B10" s="64" t="s">
+        <v>652</v>
+      </c>
+      <c r="C10" s="64">
+        <v>5.8</v>
+      </c>
+      <c r="D10" s="99"/>
+      <c r="E10" s="64">
+        <v>31</v>
+      </c>
+      <c r="F10" s="64" t="s">
+        <v>523</v>
+      </c>
+      <c r="G10" s="64">
+        <v>19.239999999999998</v>
+      </c>
+      <c r="H10" s="99"/>
+      <c r="I10" s="64">
+        <v>61</v>
+      </c>
+      <c r="J10" s="64" t="s">
+        <v>542</v>
+      </c>
+      <c r="K10" s="64">
+        <v>19.260000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="54">
+        <v>6</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>653</v>
+      </c>
+      <c r="C11" s="54">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="D11" s="99"/>
+      <c r="E11" s="54">
+        <v>32</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>562</v>
+      </c>
+      <c r="G11" s="54">
+        <v>19.829999999999998</v>
+      </c>
+      <c r="H11" s="99"/>
+      <c r="I11" s="54">
+        <v>62</v>
+      </c>
+      <c r="J11" s="54" t="s">
+        <v>574</v>
+      </c>
+      <c r="K11" s="54">
+        <v>19.829999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="64">
+        <v>7</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>654</v>
+      </c>
+      <c r="C12" s="64">
+        <v>12.2</v>
+      </c>
+      <c r="D12" s="99"/>
+      <c r="E12" s="64">
+        <v>33</v>
+      </c>
+      <c r="F12" s="64" t="s">
+        <v>524</v>
+      </c>
+      <c r="G12" s="64">
+        <v>10.25</v>
+      </c>
+      <c r="H12" s="99"/>
+      <c r="I12" s="64">
+        <v>63</v>
+      </c>
+      <c r="J12" s="64" t="s">
+        <v>543</v>
+      </c>
+      <c r="K12" s="64">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="54">
+        <v>8</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>655</v>
+      </c>
+      <c r="C13" s="54">
+        <v>7.5</v>
+      </c>
+      <c r="D13" s="99"/>
+      <c r="E13" s="54">
+        <v>34</v>
+      </c>
+      <c r="F13" s="54" t="s">
+        <v>525</v>
+      </c>
+      <c r="G13" s="54">
+        <v>5.44</v>
+      </c>
+      <c r="H13" s="99"/>
+      <c r="I13" s="54">
+        <v>64</v>
+      </c>
+      <c r="J13" s="54" t="s">
+        <v>544</v>
+      </c>
+      <c r="K13" s="54">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="64">
+        <v>9</v>
+      </c>
+      <c r="B14" s="64" t="s">
+        <v>656</v>
+      </c>
+      <c r="C14" s="64">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D14" s="99"/>
+      <c r="E14" s="64">
+        <v>35</v>
+      </c>
+      <c r="F14" s="64" t="s">
+        <v>537</v>
+      </c>
+      <c r="G14" s="64">
+        <v>4.55</v>
+      </c>
+      <c r="H14" s="99"/>
+      <c r="I14" s="64">
+        <v>65</v>
+      </c>
+      <c r="J14" s="64" t="s">
+        <v>547</v>
+      </c>
+      <c r="K14" s="64">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="54">
+        <v>10</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>657</v>
+      </c>
+      <c r="C15" s="54">
+        <v>8.9</v>
+      </c>
+      <c r="D15" s="99"/>
+      <c r="E15" s="54">
+        <v>36</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="G15" s="54">
+        <v>15.17</v>
+      </c>
+      <c r="H15" s="99"/>
+      <c r="I15" s="54">
+        <v>66</v>
+      </c>
+      <c r="J15" s="54" t="s">
+        <v>582</v>
+      </c>
+      <c r="K15" s="54">
+        <v>15.17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="64">
+        <v>11</v>
+      </c>
+      <c r="B16" s="64" t="s">
+        <v>658</v>
+      </c>
+      <c r="C16" s="64">
+        <v>15.2</v>
+      </c>
+      <c r="D16" s="99"/>
+      <c r="E16" s="64">
+        <v>37</v>
+      </c>
+      <c r="F16" s="64" t="s">
+        <v>563</v>
+      </c>
+      <c r="G16" s="64">
+        <v>10.79</v>
+      </c>
+      <c r="H16" s="99"/>
+      <c r="I16" s="64">
+        <v>67</v>
+      </c>
+      <c r="J16" s="64" t="s">
+        <v>575</v>
+      </c>
+      <c r="K16" s="64">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="54">
+        <v>12</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>659</v>
+      </c>
+      <c r="C17" s="54">
+        <v>14</v>
+      </c>
+      <c r="D17" s="99"/>
+      <c r="E17" s="54">
+        <v>38</v>
+      </c>
+      <c r="F17" s="54" t="s">
+        <v>564</v>
+      </c>
+      <c r="G17" s="54">
+        <v>10.34</v>
+      </c>
+      <c r="H17" s="99"/>
+      <c r="I17" s="54">
+        <v>68</v>
+      </c>
+      <c r="J17" s="54" t="s">
+        <v>576</v>
+      </c>
+      <c r="K17" s="54">
+        <v>10.72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="64">
+        <v>13</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>660</v>
+      </c>
+      <c r="C18" s="64">
+        <v>12.1</v>
+      </c>
+      <c r="D18" s="99"/>
+      <c r="E18" s="64">
+        <v>39</v>
+      </c>
+      <c r="F18" s="64" t="s">
+        <v>531</v>
+      </c>
+      <c r="G18" s="64">
+        <v>7.99</v>
+      </c>
+      <c r="H18" s="99"/>
+      <c r="I18" s="64">
+        <v>69</v>
+      </c>
+      <c r="J18" s="54" t="s">
+        <v>545</v>
+      </c>
+      <c r="K18" s="64">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="54">
+        <v>14</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>661</v>
+      </c>
+      <c r="C19" s="54">
+        <v>15.28</v>
+      </c>
+      <c r="D19" s="99"/>
+      <c r="E19" s="54">
+        <v>40</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>532</v>
+      </c>
+      <c r="G19" s="54">
+        <v>7.6</v>
+      </c>
+      <c r="H19" s="99"/>
+      <c r="I19" s="54">
+        <v>70</v>
+      </c>
+      <c r="J19" s="54" t="s">
+        <v>546</v>
+      </c>
+      <c r="K19" s="54">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="64">
+        <v>15</v>
+      </c>
+      <c r="B20" s="64" t="s">
+        <v>662</v>
+      </c>
+      <c r="C20" s="64">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D20" s="99"/>
+      <c r="E20" s="64">
+        <v>41</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>565</v>
+      </c>
+      <c r="G20" s="64">
+        <v>10.37</v>
+      </c>
+      <c r="H20" s="99"/>
+      <c r="I20" s="64">
+        <v>71</v>
+      </c>
+      <c r="J20" s="64" t="s">
+        <v>577</v>
+      </c>
+      <c r="K20" s="64">
+        <v>9.18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="54">
+        <v>16</v>
+      </c>
+      <c r="B21" s="54" t="s">
+        <v>663</v>
+      </c>
+      <c r="C21" s="54">
+        <v>7.7</v>
+      </c>
+      <c r="D21" s="99"/>
+      <c r="E21" s="54">
+        <v>42</v>
+      </c>
+      <c r="F21" s="54" t="s">
+        <v>566</v>
+      </c>
+      <c r="G21" s="54">
+        <v>16.13</v>
+      </c>
+      <c r="H21" s="99"/>
+      <c r="I21" s="54">
+        <v>72</v>
+      </c>
+      <c r="J21" s="54" t="s">
+        <v>578</v>
+      </c>
+      <c r="K21" s="54">
+        <v>16.13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="64">
+        <v>17</v>
+      </c>
+      <c r="B22" s="64" t="s">
+        <v>664</v>
+      </c>
+      <c r="C22" s="64">
+        <v>14.6</v>
+      </c>
+      <c r="D22" s="99"/>
+      <c r="E22" s="64">
+        <v>43</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>533</v>
+      </c>
+      <c r="G22" s="64">
+        <v>22.18</v>
+      </c>
+      <c r="H22" s="99"/>
+      <c r="I22" s="64">
+        <v>73</v>
+      </c>
+      <c r="J22" s="64" t="s">
+        <v>548</v>
+      </c>
+      <c r="K22" s="64">
+        <v>22.18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="54">
+        <v>18</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>665</v>
+      </c>
+      <c r="C23" s="54">
+        <v>12.7</v>
+      </c>
+      <c r="D23" s="99"/>
+      <c r="E23" s="54">
+        <v>44</v>
+      </c>
+      <c r="F23" s="54" t="s">
+        <v>534</v>
+      </c>
+      <c r="G23" s="54">
+        <v>4.37</v>
+      </c>
+      <c r="H23" s="99"/>
+      <c r="I23" s="54">
+        <v>74</v>
+      </c>
+      <c r="J23" s="64" t="s">
+        <v>549</v>
+      </c>
+      <c r="K23" s="54">
+        <v>25.38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="64">
+        <v>19</v>
+      </c>
+      <c r="B24" s="64" t="s">
+        <v>666</v>
+      </c>
+      <c r="C24" s="64">
+        <v>37</v>
+      </c>
+      <c r="D24" s="99"/>
+      <c r="E24" s="64">
+        <v>45</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>535</v>
+      </c>
+      <c r="G24" s="64">
+        <v>5.64</v>
+      </c>
+      <c r="H24" s="99"/>
+      <c r="I24" s="64">
+        <v>75</v>
+      </c>
+      <c r="J24" s="64" t="s">
+        <v>550</v>
+      </c>
+      <c r="K24" s="64">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="54">
+        <v>20</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>667</v>
+      </c>
+      <c r="C25" s="54">
+        <v>7.4</v>
+      </c>
+      <c r="D25" s="99"/>
+      <c r="E25" s="54">
+        <v>46</v>
+      </c>
+      <c r="F25" s="54" t="s">
+        <v>536</v>
+      </c>
+      <c r="G25" s="54">
+        <v>25.37</v>
+      </c>
+      <c r="H25" s="99"/>
+      <c r="I25" s="54">
+        <v>76</v>
+      </c>
+      <c r="J25" s="64" t="s">
+        <v>551</v>
+      </c>
+      <c r="K25" s="54">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="64">
+        <v>21</v>
+      </c>
+      <c r="B26" s="64" t="s">
+        <v>668</v>
+      </c>
+      <c r="C26" s="64">
+        <v>117.2</v>
+      </c>
+      <c r="D26" s="99"/>
+      <c r="E26" s="64">
+        <v>47</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>535</v>
+      </c>
+      <c r="G26" s="64">
+        <v>5.64</v>
+      </c>
+      <c r="H26" s="99"/>
+      <c r="I26" s="64">
+        <v>77</v>
+      </c>
+      <c r="J26" s="64" t="s">
+        <v>579</v>
+      </c>
+      <c r="K26" s="64">
+        <v>9.07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="54">
+        <v>22</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>669</v>
+      </c>
+      <c r="C27" s="54">
+        <v>20.7</v>
+      </c>
+      <c r="D27" s="99"/>
+      <c r="E27" s="54">
+        <v>48</v>
+      </c>
+      <c r="F27" s="54" t="s">
+        <v>536</v>
+      </c>
+      <c r="G27" s="54">
+        <v>25.37</v>
+      </c>
+      <c r="H27" s="99"/>
+      <c r="I27" s="54">
+        <v>78</v>
+      </c>
+      <c r="J27" s="64" t="s">
+        <v>580</v>
+      </c>
+      <c r="K27" s="54">
+        <v>15.38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="64">
+        <v>23</v>
+      </c>
+      <c r="B28" s="64" t="s">
+        <v>670</v>
+      </c>
+      <c r="C28" s="64">
+        <v>37.4</v>
+      </c>
+      <c r="D28" s="99"/>
+      <c r="E28" s="64">
+        <v>49</v>
+      </c>
+      <c r="F28" s="64" t="s">
+        <v>567</v>
+      </c>
+      <c r="G28" s="64">
+        <v>9.07</v>
+      </c>
+      <c r="H28" s="99"/>
+      <c r="I28" s="64">
+        <v>79</v>
+      </c>
+      <c r="J28" s="64" t="s">
+        <v>581</v>
+      </c>
+      <c r="K28" s="64">
+        <v>11.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="54">
+        <v>24</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>671</v>
+      </c>
+      <c r="C29" s="54">
+        <v>13.1</v>
+      </c>
+      <c r="D29" s="99"/>
+      <c r="E29" s="54">
+        <v>50</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>526</v>
+      </c>
+      <c r="G29" s="54">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="H29" s="99"/>
+      <c r="J29" s="51" t="s">
+        <v>630</v>
+      </c>
+      <c r="K29" s="85">
+        <f>SUM(K6:K28)</f>
+        <v>280.46999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="64">
+        <v>25</v>
+      </c>
+      <c r="B30" s="64" t="s">
+        <v>672</v>
+      </c>
+      <c r="C30" s="64">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D30" s="99"/>
+      <c r="E30" s="64">
+        <v>51</v>
+      </c>
+      <c r="F30" s="64" t="s">
+        <v>527</v>
+      </c>
+      <c r="G30" s="64">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="H30" s="99"/>
+      <c r="I30" s="99"/>
+      <c r="J30" s="99"/>
+      <c r="K30" s="99"/>
+    </row>
+    <row r="31" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="54">
+        <v>26</v>
+      </c>
+      <c r="B31" s="54" t="s">
+        <v>673</v>
+      </c>
+      <c r="C31" s="54">
+        <v>104</v>
+      </c>
+      <c r="D31" s="99"/>
+      <c r="E31" s="54">
+        <v>52</v>
+      </c>
+      <c r="F31" s="54" t="s">
+        <v>530</v>
+      </c>
+      <c r="G31" s="54">
+        <v>8.89</v>
+      </c>
+      <c r="H31" s="99"/>
+      <c r="I31" s="99"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="99"/>
+    </row>
+    <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="51" t="s">
+        <v>630</v>
+      </c>
+      <c r="C32" s="85">
+        <f>SUM(C6:C31)</f>
+        <v>592.27999999999986</v>
+      </c>
+      <c r="D32" s="99"/>
+      <c r="E32" s="64">
+        <v>53</v>
+      </c>
+      <c r="F32" s="64" t="s">
+        <v>456</v>
+      </c>
+      <c r="G32" s="64">
+        <v>9.69</v>
+      </c>
+      <c r="H32" s="99"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="99"/>
+      <c r="K32" s="99"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="114"/>
+      <c r="B33" s="114"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="54">
+        <v>54</v>
+      </c>
+      <c r="F33" s="54" t="s">
+        <v>538</v>
+      </c>
+      <c r="G33" s="54">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="H33" s="99"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="99"/>
+      <c r="K33" s="99"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="114"/>
+      <c r="B34" s="114"/>
+      <c r="C34" s="114"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="64">
+        <v>55</v>
+      </c>
+      <c r="F34" s="64" t="s">
+        <v>528</v>
+      </c>
+      <c r="G34" s="64">
+        <v>19.78</v>
+      </c>
+      <c r="H34" s="99"/>
+      <c r="I34" s="99"/>
+      <c r="J34" s="99"/>
+      <c r="K34" s="99"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="114"/>
+      <c r="B35" s="114"/>
+      <c r="C35" s="114"/>
+      <c r="D35" s="99"/>
+      <c r="E35" s="54">
+        <v>56</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>529</v>
+      </c>
+      <c r="G35" s="54">
+        <v>8.25</v>
+      </c>
+      <c r="H35" s="99"/>
+      <c r="I35" s="99"/>
+      <c r="J35" s="99"/>
+      <c r="K35" s="99"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="114"/>
+      <c r="B36" s="114"/>
+      <c r="C36" s="114"/>
+      <c r="D36" s="99"/>
+      <c r="F36" s="51" t="s">
+        <v>630</v>
+      </c>
+      <c r="G36" s="85">
+        <f>SUM(G6:G35)</f>
+        <v>362.54999999999995</v>
+      </c>
+      <c r="H36" s="99"/>
+      <c r="I36" s="99"/>
+      <c r="J36" s="99"/>
+      <c r="K36" s="99"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="H5:H36"/>
+    <mergeCell ref="D5:D36"/>
+    <mergeCell ref="A33:C36"/>
+    <mergeCell ref="I30:K36"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="H3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -20829,17 +21956,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -20847,18 +21974,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="100" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -20870,18 +21997,18 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="102" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="103"/>
+      <c r="I3" s="104"/>
       <c r="J3" s="68" t="s">
         <v>20</v>
       </c>
@@ -20900,14 +22027,14 @@
       <c r="C4" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="64" t="s">
@@ -20919,14 +22046,14 @@
       <c r="C5" s="64">
         <v>80.599999999999994</v>
       </c>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
@@ -20938,14 +22065,14 @@
       <c r="C6" s="54">
         <v>64.8</v>
       </c>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
@@ -20957,14 +22084,14 @@
       <c r="C7" s="54">
         <v>45.7</v>
       </c>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64" t="s">
@@ -20976,14 +22103,14 @@
       <c r="C8" s="64">
         <v>18.899999999999999</v>
       </c>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
@@ -20995,14 +22122,14 @@
       <c r="C9" s="54">
         <v>63.3</v>
       </c>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="64" t="s">
@@ -21014,14 +22141,14 @@
       <c r="C10" s="64">
         <v>64.3</v>
       </c>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="54" t="s">
@@ -21033,14 +22160,14 @@
       <c r="C11" s="54">
         <v>64.900000000000006</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="64" t="s">
@@ -21052,14 +22179,14 @@
       <c r="C12" s="64">
         <v>63.5</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="54" t="s">
@@ -21071,14 +22198,14 @@
       <c r="C13" s="54">
         <v>64</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="54" t="s">
@@ -21090,14 +22217,14 @@
       <c r="C14" s="54">
         <v>89</v>
       </c>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="99"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="64" t="s">
@@ -21109,14 +22236,14 @@
       <c r="C15" s="64">
         <v>62.5</v>
       </c>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="98"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="98"/>
-      <c r="K15" s="98"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="54" t="s">
@@ -21128,14 +22255,14 @@
       <c r="C16" s="54">
         <v>64.5</v>
       </c>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
     </row>
     <row r="17" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="64" t="s">
@@ -21147,14 +22274,14 @@
       <c r="C17" s="64">
         <v>64.2</v>
       </c>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
     </row>
     <row r="18" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="51" t="s">
@@ -21164,14 +22291,14 @@
         <f>SUM(C5:C17)</f>
         <v>810.2</v>
       </c>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="98"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="99"/>
+      <c r="H18" s="99"/>
+      <c r="I18" s="99"/>
+      <c r="J18" s="99"/>
+      <c r="K18" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -21207,36 +22334,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="111" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
     </row>
     <row r="2" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="100" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -21248,18 +22375,18 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="102" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="103"/>
+      <c r="I3" s="104"/>
       <c r="J3" s="68" t="s">
         <v>20</v>
       </c>
@@ -21278,14 +22405,14 @@
       <c r="C4" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="76" t="s">
@@ -21297,14 +22424,14 @@
       <c r="C5" s="76">
         <v>82.2</v>
       </c>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="77" t="s">
@@ -21316,14 +22443,14 @@
       <c r="C6" s="77">
         <v>63.6</v>
       </c>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="76" t="s">
@@ -21335,14 +22462,14 @@
       <c r="C7" s="76">
         <v>85.1</v>
       </c>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="77" t="s">
@@ -21354,14 +22481,14 @@
       <c r="C8" s="77">
         <v>103.5</v>
       </c>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="76" t="s">
@@ -21373,14 +22500,14 @@
       <c r="C9" s="76">
         <v>90.3</v>
       </c>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="76" t="s">
@@ -21392,14 +22519,14 @@
       <c r="C10" s="76">
         <v>63.3</v>
       </c>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="77" t="s">
@@ -21411,14 +22538,14 @@
       <c r="C11" s="77">
         <v>64</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="76" t="s">
@@ -21430,14 +22557,14 @@
       <c r="C12" s="76">
         <v>90.9</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
@@ -21449,14 +22576,14 @@
       <c r="C13" s="77">
         <v>63.8</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="76" t="s">
@@ -21468,14 +22595,14 @@
       <c r="C14" s="76">
         <v>63.9</v>
       </c>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="99"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="77" t="s">
@@ -21487,14 +22614,14 @@
       <c r="C15" s="77">
         <v>64.5</v>
       </c>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="98"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="98"/>
-      <c r="K15" s="98"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="76" t="s">
@@ -21506,14 +22633,14 @@
       <c r="C16" s="76">
         <v>64.400000000000006</v>
       </c>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
     </row>
     <row r="17" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="75" t="s">
@@ -21523,14 +22650,14 @@
         <f>SUM(C5:C16)</f>
         <v>899.49999999999989</v>
       </c>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -21552,17 +22679,17 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -21570,18 +22697,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="100" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -21593,18 +22720,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="102" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="103"/>
+      <c r="I3" s="104"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -22362,36 +23489,36 @@
       <c r="K41" s="81"/>
     </row>
     <row r="43" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="110" t="s">
+      <c r="A43" s="111" t="s">
         <v>625</v>
       </c>
-      <c r="B43" s="111"/>
-      <c r="C43" s="111"/>
-      <c r="D43" s="111"/>
-      <c r="E43" s="111"/>
-      <c r="F43" s="111"/>
-      <c r="G43" s="111"/>
-      <c r="H43" s="111"/>
-      <c r="I43" s="111"/>
-      <c r="J43" s="111"/>
-      <c r="K43" s="111"/>
+      <c r="B43" s="112"/>
+      <c r="C43" s="112"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="112"/>
+      <c r="H43" s="112"/>
+      <c r="I43" s="112"/>
+      <c r="J43" s="112"/>
+      <c r="K43" s="112"/>
     </row>
     <row r="44" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B44" s="104" t="s">
+      <c r="B44" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="105"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="105"/>
-      <c r="G44" s="106"/>
-      <c r="H44" s="100" t="s">
+      <c r="C44" s="106"/>
+      <c r="D44" s="106"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="107"/>
+      <c r="H44" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I44" s="101"/>
+      <c r="I44" s="102"/>
       <c r="J44" s="67" t="s">
         <v>5</v>
       </c>
@@ -22403,18 +23530,18 @@
       <c r="A45" s="89">
         <v>1</v>
       </c>
-      <c r="B45" s="107" t="s">
+      <c r="B45" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="108"/>
-      <c r="D45" s="108"/>
-      <c r="E45" s="108"/>
-      <c r="F45" s="108"/>
-      <c r="G45" s="109"/>
-      <c r="H45" s="102" t="s">
+      <c r="C45" s="109"/>
+      <c r="D45" s="109"/>
+      <c r="E45" s="109"/>
+      <c r="F45" s="109"/>
+      <c r="G45" s="110"/>
+      <c r="H45" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="I45" s="103"/>
+      <c r="I45" s="104"/>
       <c r="J45" s="89" t="s">
         <v>20</v>
       </c>
@@ -22964,17 +24091,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -22982,18 +24109,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="100" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -23005,18 +24132,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>413</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="112" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="113" t="s">
         <v>644</v>
       </c>
-      <c r="I3" s="103"/>
+      <c r="I3" s="104"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -23029,18 +24156,18 @@
       <c r="A4" s="89">
         <v>2</v>
       </c>
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="108" t="s">
         <v>387</v>
       </c>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="112" t="s">
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="113" t="s">
         <v>643</v>
       </c>
-      <c r="I4" s="103"/>
+      <c r="I4" s="104"/>
       <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
@@ -23050,17 +24177,17 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="97"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
     </row>
     <row r="6" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="69" t="s">
@@ -23072,7 +24199,7 @@
       <c r="C6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D6" s="98"/>
+      <c r="D6" s="99"/>
       <c r="E6" s="69" t="s">
         <v>627</v>
       </c>
@@ -23082,10 +24209,10 @@
       <c r="G6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
@@ -23097,7 +24224,7 @@
       <c r="C7" s="54">
         <v>10.5</v>
       </c>
-      <c r="D7" s="98"/>
+      <c r="D7" s="99"/>
       <c r="E7" s="64" t="s">
         <v>522</v>
       </c>
@@ -23107,10 +24234,10 @@
       <c r="G7" s="84">
         <v>4.8</v>
       </c>
-      <c r="H7" s="113"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="114"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64" t="s">
@@ -23122,7 +24249,7 @@
       <c r="C8" s="64">
         <v>22.3</v>
       </c>
-      <c r="D8" s="98"/>
+      <c r="D8" s="99"/>
       <c r="E8" s="54" t="s">
         <v>532</v>
       </c>
@@ -23132,10 +24259,10 @@
       <c r="G8" s="83">
         <v>7.5</v>
       </c>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="113"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="114"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
@@ -23147,7 +24274,7 @@
       <c r="C9" s="54">
         <v>19</v>
       </c>
-      <c r="D9" s="98"/>
+      <c r="D9" s="99"/>
       <c r="E9" s="54" t="s">
         <v>537</v>
       </c>
@@ -23157,10 +24284,10 @@
       <c r="G9" s="83">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="113"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="114"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
@@ -23172,7 +24299,7 @@
       <c r="C10" s="54">
         <v>10.1</v>
       </c>
-      <c r="D10" s="98"/>
+      <c r="D10" s="99"/>
       <c r="E10" s="81"/>
       <c r="F10" s="81" t="s">
         <v>630</v>
@@ -23181,10 +24308,10 @@
         <f>SUM(G7:G9)</f>
         <v>16.899999999999999</v>
       </c>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="113"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
@@ -23196,14 +24323,14 @@
       <c r="C11" s="64">
         <v>5.6</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="113"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
@@ -23215,14 +24342,14 @@
       <c r="C12" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113"/>
-      <c r="K12" s="113"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="114"/>
+      <c r="I12" s="114"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="114"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="64" t="s">
@@ -23234,14 +24361,14 @@
       <c r="C13" s="64">
         <v>15.7</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="113"/>
-      <c r="K13" s="113"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="114"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="114"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="51" t="s">
@@ -23251,14 +24378,14 @@
         <f>SUM(C7:C13)</f>
         <v>91.4</v>
       </c>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -23298,17 +24425,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -23316,18 +24443,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="100" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="101" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="101"/>
+      <c r="I2" s="102"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -23339,18 +24466,18 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>413</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="112" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="113" t="s">
         <v>632</v>
       </c>
-      <c r="I3" s="103"/>
+      <c r="I3" s="104"/>
       <c r="J3" s="79" t="s">
         <v>20</v>
       </c>
@@ -23363,18 +24490,18 @@
       <c r="A4" s="79">
         <v>2</v>
       </c>
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="108" t="s">
         <v>387</v>
       </c>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="112" t="s">
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="113" t="s">
         <v>633</v>
       </c>
-      <c r="I4" s="103"/>
+      <c r="I4" s="104"/>
       <c r="J4" s="79" t="s">
         <v>20</v>
       </c>
@@ -23384,17 +24511,17 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="97"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
     </row>
     <row r="6" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="69" t="s">
@@ -23406,7 +24533,7 @@
       <c r="C6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D6" s="98"/>
+      <c r="D6" s="99"/>
       <c r="E6" s="69" t="s">
         <v>627</v>
       </c>
@@ -23416,10 +24543,10 @@
       <c r="G6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
@@ -23431,7 +24558,7 @@
       <c r="C7" s="54">
         <v>9.6</v>
       </c>
-      <c r="D7" s="98"/>
+      <c r="D7" s="99"/>
       <c r="E7" s="64" t="s">
         <v>540</v>
       </c>
@@ -23441,10 +24568,10 @@
       <c r="G7" s="84">
         <v>4.8</v>
       </c>
-      <c r="H7" s="113"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="114"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64" t="s">
@@ -23456,7 +24583,7 @@
       <c r="C8" s="64">
         <v>21.9</v>
       </c>
-      <c r="D8" s="98"/>
+      <c r="D8" s="99"/>
       <c r="E8" s="54" t="s">
         <v>546</v>
       </c>
@@ -23466,10 +24593,10 @@
       <c r="G8" s="83">
         <v>7.5</v>
       </c>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="113"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="114"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
@@ -23481,7 +24608,7 @@
       <c r="C9" s="54">
         <v>19.600000000000001</v>
       </c>
-      <c r="D9" s="98"/>
+      <c r="D9" s="99"/>
       <c r="E9" s="64" t="s">
         <v>547</v>
       </c>
@@ -23491,10 +24618,10 @@
       <c r="G9" s="84">
         <v>4.5</v>
       </c>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="113"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="114"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
@@ -23506,7 +24633,7 @@
       <c r="C10" s="54">
         <v>10.5</v>
       </c>
-      <c r="D10" s="98"/>
+      <c r="D10" s="99"/>
       <c r="E10" s="81"/>
       <c r="F10" s="81" t="s">
         <v>630</v>
@@ -23515,10 +24642,10 @@
         <f>SUM(G7:G9)</f>
         <v>16.8</v>
       </c>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="113"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
@@ -23530,14 +24657,14 @@
       <c r="C11" s="64">
         <v>5.6</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="113"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
@@ -23549,14 +24676,14 @@
       <c r="C12" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113"/>
-      <c r="K12" s="113"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="114"/>
+      <c r="I12" s="114"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="114"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="64" t="s">
@@ -23568,14 +24695,14 @@
       <c r="C13" s="64">
         <v>15.7</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="113"/>
-      <c r="K13" s="113"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="114"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="114"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="51" t="s">
@@ -23585,14 +24712,14 @@
         <f>SUM(C7:C13)</f>
         <v>91.100000000000009</v>
       </c>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/school_2/floors/КП пол СОШ2.xlsx
+++ b/school_2/floors/КП пол СОШ2.xlsx
@@ -29,7 +29,7 @@
     <sheet name="4.1" sheetId="13" r:id="rId15"/>
     <sheet name="4.2" sheetId="14" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511" refMode="R1C1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="F3" s="105">
         <f>B9</f>
-        <v>9401.7000000000007</v>
+        <v>9341.5</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4440,7 +4440,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="104">
-        <v>4239.5</v>
+        <v>4179.3</v>
       </c>
       <c r="C7" s="108"/>
       <c r="D7" s="108"/>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="B9" s="85">
         <f>SUM(B6:B8)</f>
-        <v>9401.7000000000007</v>
+        <v>9341.5</v>
       </c>
       <c r="C9" s="108"/>
       <c r="D9" s="108"/>
@@ -5720,17 +5720,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="H6:K14"/>
     <mergeCell ref="E11:G14"/>
     <mergeCell ref="D6:D14"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -6054,17 +6054,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="E11:G14"/>
     <mergeCell ref="H6:K14"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="D6:D14"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10565,16 +10565,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="H44:I44"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="H44:I44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/school_2/floors/КП пол СОШ2.xlsx
+++ b/school_2/floors/КП пол СОШ2.xlsx
@@ -12,24 +12,25 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520"/>
   </bookViews>
   <sheets>
-    <sheet name="9.1шлфк" sheetId="21" r:id="rId1"/>
-    <sheet name="8.1_орг" sheetId="20" r:id="rId2"/>
-    <sheet name="7-Кер" sheetId="15" r:id="rId3"/>
-    <sheet name="6.3_ост" sheetId="17" r:id="rId4"/>
-    <sheet name="5.3_нал_пл" sheetId="16" r:id="rId5"/>
-    <sheet name="4.3_ост" sheetId="18" r:id="rId6"/>
-    <sheet name="КП" sheetId="3" r:id="rId7"/>
-    <sheet name="Пом" sheetId="4" r:id="rId8"/>
-    <sheet name="Лист2" sheetId="7" r:id="rId9"/>
-    <sheet name="Типы" sheetId="5" r:id="rId10"/>
-    <sheet name="5.1" sheetId="6" r:id="rId11"/>
-    <sheet name="5.2" sheetId="8" r:id="rId12"/>
-    <sheet name="6.1" sheetId="10" r:id="rId13"/>
-    <sheet name="6.2" sheetId="11" r:id="rId14"/>
-    <sheet name="4.1" sheetId="13" r:id="rId15"/>
-    <sheet name="4.2" sheetId="14" r:id="rId16"/>
+    <sheet name="9.2плтк" sheetId="22" r:id="rId1"/>
+    <sheet name="9.1шлфк" sheetId="21" r:id="rId2"/>
+    <sheet name="8.1_орг" sheetId="20" r:id="rId3"/>
+    <sheet name="7-Кер" sheetId="15" r:id="rId4"/>
+    <sheet name="6.3_ост" sheetId="17" r:id="rId5"/>
+    <sheet name="5.3_нал_пл" sheetId="16" r:id="rId6"/>
+    <sheet name="4.3_ост" sheetId="18" r:id="rId7"/>
+    <sheet name="КП" sheetId="3" r:id="rId8"/>
+    <sheet name="Пом" sheetId="4" r:id="rId9"/>
+    <sheet name="Лист2" sheetId="7" r:id="rId10"/>
+    <sheet name="Типы" sheetId="5" r:id="rId11"/>
+    <sheet name="5.1" sheetId="6" r:id="rId12"/>
+    <sheet name="5.2" sheetId="8" r:id="rId13"/>
+    <sheet name="6.1" sheetId="10" r:id="rId14"/>
+    <sheet name="6.2" sheetId="11" r:id="rId15"/>
+    <sheet name="4.1" sheetId="13" r:id="rId16"/>
+    <sheet name="4.2" sheetId="14" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="695">
   <si>
     <t>Номер п/п</t>
   </si>
@@ -2093,7 +2094,61 @@
     <t>1, 2, 3 этаж.</t>
   </si>
   <si>
-    <t>Площадь шлифования бетонных поверхностей пола 1, 2 и 3-го (снятие наплывов и швов, снятие цементного молочка)</t>
+    <t>Площадь шлифования наливного пола</t>
+  </si>
+  <si>
+    <t>1.088</t>
+  </si>
+  <si>
+    <t>ПВХ плитка и плинтус</t>
+  </si>
+  <si>
+    <t>1.032</t>
+  </si>
+  <si>
+    <t>1.084</t>
+  </si>
+  <si>
+    <t>плинтус, пог.м.</t>
+  </si>
+  <si>
+    <t>объем, м2.</t>
+  </si>
+  <si>
+    <t>пом.</t>
+  </si>
+  <si>
+    <t>№ п.п</t>
+  </si>
+  <si>
+    <t>Керамогранитная плитка и плинтус</t>
+  </si>
+  <si>
+    <t>1 этаж</t>
+  </si>
+  <si>
+    <t>Установка напольного плинтуса ПВХ</t>
+  </si>
+  <si>
+    <t>1-2 этаж</t>
+  </si>
+  <si>
+    <t>Устройство покрытия пола с затиркой и укрытием ДВП / из ПВХ плитки</t>
+  </si>
+  <si>
+    <t>Устройство покрытия пола с затиркой и укрытием ДВП / из керамогранитной плитки</t>
+  </si>
+  <si>
+    <t>Объем, м2</t>
+  </si>
+  <si>
+    <t>Наименование</t>
+  </si>
+  <si>
+    <t>Ведомость работ</t>
+  </si>
+  <si>
+    <t>Устройство плинтуса из керамогранитной плитки</t>
   </si>
 </sst>
 </file>
@@ -2107,11 +2162,19 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2304,6 +2367,24 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="ГОСТ тип А"/>
       <family val="2"/>
@@ -2632,335 +2713,407 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="25" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="25" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="25" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="25" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="30" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="24" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="24" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="24" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="2"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="39">
@@ -4345,140 +4498,342 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.21875" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" style="106" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" style="106" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="106" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="106" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="106" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="106" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="106" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="106"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
-        <v>625</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-    </row>
-    <row r="2" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="116" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="115" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="117" t="s">
+        <v>692</v>
+      </c>
+      <c r="C2" s="118"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="114" t="s">
+        <v>631</v>
+      </c>
+      <c r="F2" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="113" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="108">
+        <v>1</v>
+      </c>
+      <c r="B3" s="120" t="s">
+        <v>690</v>
+      </c>
+      <c r="C3" s="121"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="112" t="s">
+        <v>688</v>
+      </c>
+      <c r="F3" s="108" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="111">
+        <f>C16</f>
+        <v>137.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="108">
         <v>2</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="99" t="s">
-        <v>631</v>
-      </c>
-      <c r="E2" s="67" t="s">
+      <c r="B4" s="120" t="s">
+        <v>689</v>
+      </c>
+      <c r="C4" s="121"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="112" t="s">
+        <v>686</v>
+      </c>
+      <c r="F4" s="108" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="111">
+        <f>C19</f>
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="108">
+        <v>3</v>
+      </c>
+      <c r="B5" s="120" t="s">
+        <v>694</v>
+      </c>
+      <c r="C5" s="121"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="112" t="s">
+        <v>688</v>
+      </c>
+      <c r="F5" s="108" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="111">
+        <f>D16</f>
+        <v>131.20000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="108">
+        <v>4</v>
+      </c>
+      <c r="B6" s="120" t="s">
+        <v>687</v>
+      </c>
+      <c r="C6" s="121"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="112" t="s">
+        <v>686</v>
+      </c>
+      <c r="F6" s="108" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="111">
+        <f>D19</f>
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="123"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="127" t="s">
+        <v>685</v>
+      </c>
+      <c r="B8" s="127"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+      <c r="G8" s="129"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="108" t="s">
+        <v>684</v>
+      </c>
+      <c r="B9" s="108" t="s">
+        <v>683</v>
+      </c>
+      <c r="C9" s="108" t="s">
+        <v>682</v>
+      </c>
+      <c r="D9" s="108" t="s">
+        <v>681</v>
+      </c>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="108">
+        <v>1</v>
+      </c>
+      <c r="B10" s="108" t="s">
+        <v>648</v>
+      </c>
+      <c r="C10" s="107">
+        <v>25.1</v>
+      </c>
+      <c r="D10" s="107">
+        <f>19.6</f>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="108">
+        <v>2</v>
+      </c>
+      <c r="B11" s="110" t="s">
+        <v>680</v>
+      </c>
+      <c r="C11" s="107">
+        <v>23.8</v>
+      </c>
+      <c r="D11" s="107">
+        <v>20.2</v>
+      </c>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="108">
+        <v>3</v>
+      </c>
+      <c r="B12" s="108" t="s">
+        <v>654</v>
+      </c>
+      <c r="C12" s="107">
+        <v>12.1</v>
+      </c>
+      <c r="D12" s="107">
+        <v>12.2</v>
+      </c>
+      <c r="E12" s="129"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="108">
+        <v>4</v>
+      </c>
+      <c r="B13" s="108" t="s">
+        <v>679</v>
+      </c>
+      <c r="C13" s="107">
+        <v>30.8</v>
+      </c>
+      <c r="D13" s="107">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="108">
         <v>5</v>
       </c>
-      <c r="F2" s="101" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="98">
+      <c r="B14" s="108" t="s">
+        <v>557</v>
+      </c>
+      <c r="C14" s="107">
+        <f>23.6+1</f>
+        <v>24.6</v>
+      </c>
+      <c r="D14" s="107">
+        <v>24.1</v>
+      </c>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="108">
+        <v>6</v>
+      </c>
+      <c r="B15" s="108" t="s">
+        <v>556</v>
+      </c>
+      <c r="C15" s="107">
+        <f>19.7+1</f>
+        <v>20.7</v>
+      </c>
+      <c r="D15" s="107">
+        <v>20.3</v>
+      </c>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="124" t="s">
+        <v>630</v>
+      </c>
+      <c r="B16" s="125"/>
+      <c r="C16" s="109">
+        <f>SUM(C10:C15)</f>
+        <v>137.1</v>
+      </c>
+      <c r="D16" s="109">
+        <f>SUM(D10:D15)</f>
+        <v>131.20000000000002</v>
+      </c>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="128"/>
+      <c r="B17" s="128"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="129"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="126" t="s">
+        <v>678</v>
+      </c>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="108">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
-        <v>676</v>
-      </c>
-      <c r="C3" s="112"/>
-      <c r="D3" s="100" t="s">
-        <v>675</v>
-      </c>
-      <c r="E3" s="98" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="105">
-        <f>B9</f>
-        <v>9341.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="113"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-    </row>
-    <row r="5" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="69" t="s">
-        <v>674</v>
-      </c>
-      <c r="B5" s="69" t="s">
-        <v>629</v>
-      </c>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="64">
-        <v>1</v>
-      </c>
-      <c r="B6" s="103">
-        <v>1581.9</v>
-      </c>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="54">
-        <v>2</v>
-      </c>
-      <c r="B7" s="104">
-        <v>4179.3</v>
-      </c>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="64">
-        <v>3</v>
-      </c>
-      <c r="B8" s="103">
-        <v>3580.3</v>
-      </c>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-    </row>
-    <row r="9" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="102" t="s">
-        <v>630</v>
-      </c>
-      <c r="B9" s="85">
-        <f>SUM(B6:B8)</f>
-        <v>9341.5</v>
-      </c>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
+      <c r="B19" s="108" t="s">
+        <v>677</v>
+      </c>
+      <c r="C19" s="107">
+        <v>5.7</v>
+      </c>
+      <c r="D19" s="107">
+        <v>9.1</v>
+      </c>
+      <c r="E19" s="129"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="129"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C5:F9"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A4:F4"/>
+  <mergeCells count="12">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E8:G19"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -4487,6 +4842,842 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="73" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1" s="73" t="s">
+        <v>583</v>
+      </c>
+      <c r="C1" s="73" t="s">
+        <v>604</v>
+      </c>
+      <c r="D1" s="73" t="s">
+        <v>584</v>
+      </c>
+      <c r="E1" s="73" t="s">
+        <v>593</v>
+      </c>
+      <c r="F1" s="73" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="64">
+        <v>2</v>
+      </c>
+      <c r="B2" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>442</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F2" s="64">
+        <v>80.599999999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="54">
+        <v>2</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>443</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F3" s="54">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="64">
+        <v>2</v>
+      </c>
+      <c r="B4" s="64" t="s">
+        <v>607</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>444</v>
+      </c>
+      <c r="E4" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F4" s="64">
+        <v>218.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="54">
+        <v>2</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>445</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F5" s="54">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="64">
+        <v>2</v>
+      </c>
+      <c r="B6" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>446</v>
+      </c>
+      <c r="E6" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F6" s="64">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="54">
+        <v>2</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>617</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>558</v>
+      </c>
+      <c r="D7" s="54" t="s">
+        <v>557</v>
+      </c>
+      <c r="E7" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F7" s="54">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="64">
+        <v>2</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>447</v>
+      </c>
+      <c r="E8" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F8" s="64">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="54">
+        <v>2</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>448</v>
+      </c>
+      <c r="E9" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F9" s="54">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="64">
+        <v>2</v>
+      </c>
+      <c r="B10" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D10" s="64" t="s">
+        <v>449</v>
+      </c>
+      <c r="E10" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F10" s="64">
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="54">
+        <v>2</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D11" s="54" t="s">
+        <v>450</v>
+      </c>
+      <c r="E11" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F11" s="54">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="64">
+        <v>2</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>451</v>
+      </c>
+      <c r="E12" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F12" s="64">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="54">
+        <v>2</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>607</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D13" s="54" t="s">
+        <v>452</v>
+      </c>
+      <c r="E13" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F13" s="54">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="64">
+        <v>2</v>
+      </c>
+      <c r="B14" s="64" t="s">
+        <v>613</v>
+      </c>
+      <c r="C14" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D14" s="64" t="s">
+        <v>453</v>
+      </c>
+      <c r="E14" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F14" s="64">
+        <v>478.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="54">
+        <v>2</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>607</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>454</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F15" s="54">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="64">
+        <v>2</v>
+      </c>
+      <c r="B16" s="64" t="s">
+        <v>607</v>
+      </c>
+      <c r="C16" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D16" s="64" t="s">
+        <v>455</v>
+      </c>
+      <c r="E16" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F16" s="64">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="54">
+        <v>2</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>607</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>456</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F17" s="54">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="64">
+        <v>2</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C18" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D18" s="64" t="s">
+        <v>457</v>
+      </c>
+      <c r="E18" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F18" s="64">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="54">
+        <v>2</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>618</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>512</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>517</v>
+      </c>
+      <c r="E19" s="54" t="s">
+        <v>598</v>
+      </c>
+      <c r="F19" s="54">
+        <v>543.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="64">
+        <v>2</v>
+      </c>
+      <c r="B20" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>512</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>518</v>
+      </c>
+      <c r="E20" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F20" s="64">
+        <v>66.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="54">
+        <v>2</v>
+      </c>
+      <c r="B21" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D21" s="54" t="s">
+        <v>458</v>
+      </c>
+      <c r="E21" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F21" s="54">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="64">
+        <v>2</v>
+      </c>
+      <c r="B22" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C22" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>459</v>
+      </c>
+      <c r="E22" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F22" s="64">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="54">
+        <v>2</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D23" s="54" t="s">
+        <v>460</v>
+      </c>
+      <c r="E23" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F23" s="54">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="64">
+        <v>2</v>
+      </c>
+      <c r="B24" s="64" t="s">
+        <v>607</v>
+      </c>
+      <c r="C24" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="E24" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F24" s="64">
+        <v>100.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="54">
+        <v>2</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>462</v>
+      </c>
+      <c r="E25" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F25" s="52">
+        <v>218.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="64">
+        <v>2</v>
+      </c>
+      <c r="B26" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C26" s="64" t="s">
+        <v>514</v>
+      </c>
+      <c r="D26" s="64" t="s">
+        <v>462</v>
+      </c>
+      <c r="E26" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F26" s="64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="54">
+        <v>2</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>607</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>463</v>
+      </c>
+      <c r="E27" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F27" s="54">
+        <v>162.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="64">
+        <v>2</v>
+      </c>
+      <c r="B28" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C28" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>464</v>
+      </c>
+      <c r="E28" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F28" s="64">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="54">
+        <v>2</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>465</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F29" s="54">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="64">
+        <v>2</v>
+      </c>
+      <c r="B30" s="64" t="s">
+        <v>607</v>
+      </c>
+      <c r="C30" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D30" s="64" t="s">
+        <v>466</v>
+      </c>
+      <c r="E30" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F30" s="64">
+        <v>130.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="54">
+        <v>2</v>
+      </c>
+      <c r="B31" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>467</v>
+      </c>
+      <c r="E31" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F31" s="54">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="64">
+        <v>2</v>
+      </c>
+      <c r="B32" s="64" t="s">
+        <v>617</v>
+      </c>
+      <c r="C32" s="64" t="s">
+        <v>515</v>
+      </c>
+      <c r="D32" s="64" t="s">
+        <v>556</v>
+      </c>
+      <c r="E32" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F32" s="64">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="54">
+        <v>2</v>
+      </c>
+      <c r="B33" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>468</v>
+      </c>
+      <c r="E33" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F33" s="54">
+        <v>34.700000000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="64">
+        <v>2</v>
+      </c>
+      <c r="B34" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C34" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D34" s="64" t="s">
+        <v>469</v>
+      </c>
+      <c r="E34" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F34" s="64">
+        <v>168.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="54">
+        <v>2</v>
+      </c>
+      <c r="B35" s="54" t="s">
+        <v>616</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>514</v>
+      </c>
+      <c r="D35" s="54" t="s">
+        <v>469</v>
+      </c>
+      <c r="E35" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="64">
+        <v>2</v>
+      </c>
+      <c r="B36" s="64" t="s">
+        <v>607</v>
+      </c>
+      <c r="C36" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D36" s="64" t="s">
+        <v>470</v>
+      </c>
+      <c r="E36" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F36" s="64">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="54">
+        <v>2</v>
+      </c>
+      <c r="B37" s="54" t="s">
+        <v>606</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D37" s="54" t="s">
+        <v>471</v>
+      </c>
+      <c r="E37" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F37" s="54">
+        <v>66.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="64">
+        <v>2</v>
+      </c>
+      <c r="B38" s="64" t="s">
+        <v>606</v>
+      </c>
+      <c r="C38" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D38" s="64" t="s">
+        <v>472</v>
+      </c>
+      <c r="E38" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F38" s="64">
+        <v>93.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="54">
+        <v>2</v>
+      </c>
+      <c r="B39" s="54" t="s">
+        <v>607</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>440</v>
+      </c>
+      <c r="D39" s="54" t="s">
+        <v>473</v>
+      </c>
+      <c r="E39" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="F39" s="54">
+        <v>91.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="64">
+        <v>2</v>
+      </c>
+      <c r="B40" s="64" t="s">
+        <v>614</v>
+      </c>
+      <c r="C40" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="D40" s="64" t="s">
+        <v>474</v>
+      </c>
+      <c r="E40" s="64" t="s">
+        <v>595</v>
+      </c>
+      <c r="F40" s="64">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="74">
+        <v>2</v>
+      </c>
+      <c r="B41" s="74" t="s">
+        <v>607</v>
+      </c>
+      <c r="C41" s="74" t="s">
+        <v>440</v>
+      </c>
+      <c r="D41" s="74" t="s">
+        <v>475</v>
+      </c>
+      <c r="E41" s="74" t="s">
+        <v>595</v>
+      </c>
+      <c r="F41" s="74">
+        <v>129.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:G17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -4667,7 +5858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4686,17 +5877,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -4704,18 +5895,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="115"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -4727,18 +5918,18 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="129" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="153" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="128"/>
+      <c r="I3" s="152"/>
       <c r="J3" s="68" t="s">
         <v>20</v>
       </c>
@@ -4757,14 +5948,14 @@
       <c r="C4" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="64" t="s">
@@ -4776,14 +5967,14 @@
       <c r="C5" s="64">
         <v>80.599999999999994</v>
       </c>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
@@ -4795,14 +5986,14 @@
       <c r="C6" s="54">
         <v>64.8</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="132"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
@@ -4814,14 +6005,14 @@
       <c r="C7" s="54">
         <v>45.7</v>
       </c>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64" t="s">
@@ -4833,14 +6024,14 @@
       <c r="C8" s="64">
         <v>18.899999999999999</v>
       </c>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="108"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="132"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
@@ -4852,14 +6043,14 @@
       <c r="C9" s="54">
         <v>63.3</v>
       </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="108"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="64" t="s">
@@ -4871,14 +6062,14 @@
       <c r="C10" s="64">
         <v>64.3</v>
       </c>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="108"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="132"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="54" t="s">
@@ -4890,14 +6081,14 @@
       <c r="C11" s="54">
         <v>64.900000000000006</v>
       </c>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="64" t="s">
@@ -4909,14 +6100,14 @@
       <c r="C12" s="64">
         <v>63.5</v>
       </c>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="54" t="s">
@@ -4928,14 +6119,14 @@
       <c r="C13" s="54">
         <v>64</v>
       </c>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="54" t="s">
@@ -4947,14 +6138,14 @@
       <c r="C14" s="54">
         <v>89</v>
       </c>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="108"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="64" t="s">
@@ -4966,14 +6157,14 @@
       <c r="C15" s="64">
         <v>62.5</v>
       </c>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="108"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="54" t="s">
@@ -4985,14 +6176,14 @@
       <c r="C16" s="54">
         <v>64.5</v>
       </c>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="108"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="108"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="132"/>
+      <c r="K16" s="132"/>
     </row>
     <row r="17" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="64" t="s">
@@ -5004,14 +6195,14 @@
       <c r="C17" s="64">
         <v>64.2</v>
       </c>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="108"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="108"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
     </row>
     <row r="18" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="51" t="s">
@@ -5021,14 +6212,14 @@
         <f>SUM(C5:C17)</f>
         <v>810.2</v>
       </c>
-      <c r="D18" s="108"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="108"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="108"/>
-      <c r="K18" s="108"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="132"/>
+      <c r="K18" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5044,7 +6235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -5064,36 +6255,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
     </row>
     <row r="2" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="115"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -5105,18 +6296,18 @@
       <c r="A3" s="68">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="129" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="128"/>
+      <c r="I3" s="152"/>
       <c r="J3" s="68" t="s">
         <v>20</v>
       </c>
@@ -5135,14 +6326,14 @@
       <c r="C4" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="76" t="s">
@@ -5154,14 +6345,14 @@
       <c r="C5" s="76">
         <v>82.2</v>
       </c>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="77" t="s">
@@ -5173,14 +6364,14 @@
       <c r="C6" s="77">
         <v>63.6</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="132"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="76" t="s">
@@ -5192,14 +6383,14 @@
       <c r="C7" s="76">
         <v>85.1</v>
       </c>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="77" t="s">
@@ -5211,14 +6402,14 @@
       <c r="C8" s="77">
         <v>103.5</v>
       </c>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="108"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="132"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="76" t="s">
@@ -5230,14 +6421,14 @@
       <c r="C9" s="76">
         <v>90.3</v>
       </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="108"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="76" t="s">
@@ -5249,14 +6440,14 @@
       <c r="C10" s="76">
         <v>63.3</v>
       </c>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="108"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="132"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="77" t="s">
@@ -5268,14 +6459,14 @@
       <c r="C11" s="77">
         <v>64</v>
       </c>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="76" t="s">
@@ -5287,14 +6478,14 @@
       <c r="C12" s="76">
         <v>90.9</v>
       </c>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
@@ -5306,14 +6497,14 @@
       <c r="C13" s="77">
         <v>63.8</v>
       </c>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="76" t="s">
@@ -5325,14 +6516,14 @@
       <c r="C14" s="76">
         <v>63.9</v>
       </c>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="108"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="77" t="s">
@@ -5344,14 +6535,14 @@
       <c r="C15" s="77">
         <v>64.5</v>
       </c>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="108"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="76" t="s">
@@ -5363,14 +6554,14 @@
       <c r="C16" s="76">
         <v>64.400000000000006</v>
       </c>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="108"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="108"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="132"/>
+      <c r="K16" s="132"/>
     </row>
     <row r="17" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="75" t="s">
@@ -5380,14 +6571,14 @@
         <f>SUM(C5:C16)</f>
         <v>899.49999999999989</v>
       </c>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="108"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="108"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5397,340 +6588,6 @@
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="H3:I3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.21875" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" customWidth="1"/>
-    <col min="4" max="4" width="4.109375" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
-        <v>625</v>
-      </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-    </row>
-    <row r="2" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
-        <v>626</v>
-      </c>
-      <c r="B2" s="109" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
-        <v>631</v>
-      </c>
-      <c r="I2" s="115"/>
-      <c r="J2" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="71" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="89">
-        <v>1</v>
-      </c>
-      <c r="B3" s="111" t="s">
-        <v>413</v>
-      </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="127" t="s">
-        <v>644</v>
-      </c>
-      <c r="I3" s="128"/>
-      <c r="J3" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="72">
-        <f>C14</f>
-        <v>91.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="89">
-        <v>2</v>
-      </c>
-      <c r="B4" s="111" t="s">
-        <v>387</v>
-      </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="127" t="s">
-        <v>643</v>
-      </c>
-      <c r="I4" s="128"/>
-      <c r="J4" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="72">
-        <f>G10</f>
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="113"/>
-      <c r="B5" s="113"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-    </row>
-    <row r="6" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="69" t="s">
-        <v>627</v>
-      </c>
-      <c r="B6" s="69" t="s">
-        <v>628</v>
-      </c>
-      <c r="C6" s="69" t="s">
-        <v>629</v>
-      </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="69" t="s">
-        <v>627</v>
-      </c>
-      <c r="F6" s="69" t="s">
-        <v>628</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>629</v>
-      </c>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="119"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="54" t="s">
-        <v>561</v>
-      </c>
-      <c r="B7" s="54" t="s">
-        <v>592</v>
-      </c>
-      <c r="C7" s="54">
-        <v>10.5</v>
-      </c>
-      <c r="D7" s="108"/>
-      <c r="E7" s="64" t="s">
-        <v>522</v>
-      </c>
-      <c r="F7" s="64" t="s">
-        <v>594</v>
-      </c>
-      <c r="G7" s="84">
-        <v>4.8</v>
-      </c>
-      <c r="H7" s="119"/>
-      <c r="I7" s="119"/>
-      <c r="J7" s="119"/>
-      <c r="K7" s="119"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="64" t="s">
-        <v>521</v>
-      </c>
-      <c r="B8" s="64" t="s">
-        <v>592</v>
-      </c>
-      <c r="C8" s="64">
-        <v>22.3</v>
-      </c>
-      <c r="D8" s="108"/>
-      <c r="E8" s="54" t="s">
-        <v>532</v>
-      </c>
-      <c r="F8" s="54" t="s">
-        <v>594</v>
-      </c>
-      <c r="G8" s="83">
-        <v>7.5</v>
-      </c>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="119"/>
-      <c r="K8" s="119"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="54" t="s">
-        <v>523</v>
-      </c>
-      <c r="B9" s="54" t="s">
-        <v>592</v>
-      </c>
-      <c r="C9" s="54">
-        <v>19</v>
-      </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="54" t="s">
-        <v>537</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>594</v>
-      </c>
-      <c r="G9" s="83">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54" t="s">
-        <v>524</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>592</v>
-      </c>
-      <c r="C10" s="54">
-        <v>10.1</v>
-      </c>
-      <c r="D10" s="108"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81" t="s">
-        <v>630</v>
-      </c>
-      <c r="G10" s="81">
-        <f>SUM(G7:G9)</f>
-        <v>16.899999999999999</v>
-      </c>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64" t="s">
-        <v>525</v>
-      </c>
-      <c r="B11" s="64" t="s">
-        <v>592</v>
-      </c>
-      <c r="C11" s="64">
-        <v>5.6</v>
-      </c>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="119"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54" t="s">
-        <v>531</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>592</v>
-      </c>
-      <c r="C12" s="54">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="119"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64" t="s">
-        <v>571</v>
-      </c>
-      <c r="B13" s="64" t="s">
-        <v>592</v>
-      </c>
-      <c r="C13" s="64">
-        <v>15.7</v>
-      </c>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="119"/>
-      <c r="I13" s="119"/>
-      <c r="J13" s="119"/>
-      <c r="K13" s="119"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="51" t="s">
-        <v>630</v>
-      </c>
-      <c r="C14" s="85">
-        <f>SUM(C7:C13)</f>
-        <v>91.4</v>
-      </c>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="119"/>
-      <c r="K14" s="119"/>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H6:K14"/>
-    <mergeCell ref="E11:G14"/>
-    <mergeCell ref="D6:D14"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="H4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -5756,17 +6613,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -5774,18 +6631,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="115"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -5794,65 +6651,65 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="79">
+      <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="135" t="s">
         <v>413</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="127" t="s">
-        <v>632</v>
-      </c>
-      <c r="I3" s="128"/>
-      <c r="J3" s="79" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="151" t="s">
+        <v>644</v>
+      </c>
+      <c r="I3" s="152"/>
+      <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
       <c r="K3" s="72">
         <f>C14</f>
-        <v>91.100000000000009</v>
+        <v>91.4</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="79">
+      <c r="A4" s="89">
         <v>2</v>
       </c>
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="135" t="s">
         <v>387</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="127" t="s">
-        <v>633</v>
-      </c>
-      <c r="I4" s="128"/>
-      <c r="J4" s="79" t="s">
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="151" t="s">
+        <v>643</v>
+      </c>
+      <c r="I4" s="152"/>
+      <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
       <c r="K4" s="72">
         <f>G10</f>
-        <v>16.8</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="113"/>
-      <c r="B5" s="113"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
+      <c r="A5" s="137"/>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="137"/>
+      <c r="K5" s="137"/>
     </row>
     <row r="6" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="69" t="s">
@@ -5864,7 +6721,7 @@
       <c r="C6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D6" s="108"/>
+      <c r="D6" s="132"/>
       <c r="E6" s="69" t="s">
         <v>627</v>
       </c>
@@ -5874,24 +6731,24 @@
       <c r="G6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="119"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="B7" s="54" t="s">
         <v>592</v>
       </c>
       <c r="C7" s="54">
-        <v>9.6</v>
-      </c>
-      <c r="D7" s="108"/>
+        <v>10.5</v>
+      </c>
+      <c r="D7" s="132"/>
       <c r="E7" s="64" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="F7" s="64" t="s">
         <v>594</v>
@@ -5899,24 +6756,24 @@
       <c r="G7" s="84">
         <v>4.8</v>
       </c>
-      <c r="H7" s="119"/>
-      <c r="I7" s="119"/>
-      <c r="J7" s="119"/>
-      <c r="K7" s="119"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="143"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64" t="s">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="B8" s="64" t="s">
         <v>592</v>
       </c>
       <c r="C8" s="64">
-        <v>21.9</v>
-      </c>
-      <c r="D8" s="108"/>
+        <v>22.3</v>
+      </c>
+      <c r="D8" s="132"/>
       <c r="E8" s="54" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="F8" s="54" t="s">
         <v>594</v>
@@ -5924,63 +6781,63 @@
       <c r="G8" s="83">
         <v>7.5</v>
       </c>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="119"/>
-      <c r="K8" s="119"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="143"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="B9" s="54" t="s">
         <v>592</v>
       </c>
       <c r="C9" s="54">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="64" t="s">
-        <v>547</v>
-      </c>
-      <c r="F9" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="132"/>
+      <c r="E9" s="54" t="s">
+        <v>537</v>
+      </c>
+      <c r="F9" s="54" t="s">
         <v>594</v>
       </c>
-      <c r="G9" s="84">
-        <v>4.5</v>
-      </c>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
+      <c r="G9" s="83">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H9" s="143"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
-        <v>543</v>
+        <v>524</v>
       </c>
       <c r="B10" s="54" t="s">
         <v>592</v>
       </c>
       <c r="C10" s="54">
-        <v>10.5</v>
-      </c>
-      <c r="D10" s="108"/>
+        <v>10.1</v>
+      </c>
+      <c r="D10" s="132"/>
       <c r="E10" s="81"/>
       <c r="F10" s="81" t="s">
         <v>630</v>
       </c>
       <c r="G10" s="81">
         <f>SUM(G7:G9)</f>
-        <v>16.8</v>
-      </c>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
+        <v>16.899999999999999</v>
+      </c>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="143"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="B11" s="64" t="s">
         <v>592</v>
@@ -5988,18 +6845,18 @@
       <c r="C11" s="64">
         <v>5.6</v>
       </c>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="119"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="B12" s="54" t="s">
         <v>592</v>
@@ -6007,18 +6864,18 @@
       <c r="C12" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="119"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="143"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="64" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="B13" s="64" t="s">
         <v>592</v>
@@ -6026,14 +6883,14 @@
       <c r="C13" s="64">
         <v>15.7</v>
       </c>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="119"/>
-      <c r="I13" s="119"/>
-      <c r="J13" s="119"/>
-      <c r="K13" s="119"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="51" t="s">
@@ -6041,30 +6898,30 @@
       </c>
       <c r="C14" s="85">
         <f>SUM(C7:C13)</f>
-        <v>91.100000000000009</v>
-      </c>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="119"/>
-      <c r="K14" s="119"/>
+        <v>91.4</v>
+      </c>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="H6:K14"/>
+    <mergeCell ref="E11:G14"/>
+    <mergeCell ref="D6:D14"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="H4:I4"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="E11:G14"/>
-    <mergeCell ref="H6:K14"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="D6:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -6073,7 +6930,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.21875" customWidth="1"/>
@@ -6090,17 +6947,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -6108,18 +6965,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="115"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -6131,217 +6988,269 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="120" t="s">
-        <v>636</v>
-      </c>
-      <c r="I3" s="130"/>
+      <c r="B3" s="135" t="s">
+        <v>413</v>
+      </c>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="151" t="s">
+        <v>632</v>
+      </c>
+      <c r="I3" s="152"/>
       <c r="J3" s="79" t="s">
         <v>20</v>
       </c>
       <c r="K3" s="72">
-        <f>C13</f>
-        <v>84.199999999999989</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="69" t="s">
+        <f>C14</f>
+        <v>91.100000000000009</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="79">
+        <v>2</v>
+      </c>
+      <c r="B4" s="135" t="s">
+        <v>387</v>
+      </c>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="151" t="s">
+        <v>633</v>
+      </c>
+      <c r="I4" s="152"/>
+      <c r="J4" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="72">
+        <f>G10</f>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="137"/>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="137"/>
+      <c r="K5" s="137"/>
+    </row>
+    <row r="6" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="69" t="s">
         <v>627</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B6" s="69" t="s">
         <v>628</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C6" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="64" t="s">
-        <v>521</v>
-      </c>
-      <c r="B5" s="64" t="s">
-        <v>513</v>
-      </c>
-      <c r="C5" s="64">
-        <v>23.5</v>
-      </c>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="54" t="s">
-        <v>522</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>513</v>
-      </c>
-      <c r="C6" s="54">
+      <c r="D6" s="132"/>
+      <c r="E6" s="69" t="s">
+        <v>627</v>
+      </c>
+      <c r="F6" s="69" t="s">
+        <v>628</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>629</v>
+      </c>
+      <c r="H6" s="143"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="54" t="s">
+        <v>573</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>592</v>
+      </c>
+      <c r="C7" s="54">
+        <v>9.6</v>
+      </c>
+      <c r="D7" s="132"/>
+      <c r="E7" s="64" t="s">
+        <v>540</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>594</v>
+      </c>
+      <c r="G7" s="84">
         <v>4.8</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="64" t="s">
-        <v>523</v>
-      </c>
-      <c r="B7" s="64" t="s">
-        <v>513</v>
-      </c>
-      <c r="C7" s="64">
-        <v>19.5</v>
-      </c>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="143"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="54" t="s">
-        <v>524</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>513</v>
-      </c>
-      <c r="C8" s="54">
-        <v>10.3</v>
-      </c>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="108"/>
+      <c r="A8" s="64" t="s">
+        <v>541</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>592</v>
+      </c>
+      <c r="C8" s="64">
+        <v>21.9</v>
+      </c>
+      <c r="D8" s="132"/>
+      <c r="E8" s="54" t="s">
+        <v>546</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>594</v>
+      </c>
+      <c r="G8" s="83">
+        <v>7.5</v>
+      </c>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="143"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="64" t="s">
-        <v>525</v>
-      </c>
-      <c r="B9" s="64" t="s">
-        <v>513</v>
-      </c>
-      <c r="C9" s="64">
-        <v>5.6</v>
-      </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="108"/>
+      <c r="A9" s="54" t="s">
+        <v>542</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>592</v>
+      </c>
+      <c r="C9" s="54">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D9" s="132"/>
+      <c r="E9" s="64" t="s">
+        <v>547</v>
+      </c>
+      <c r="F9" s="64" t="s">
+        <v>594</v>
+      </c>
+      <c r="G9" s="84">
+        <v>4.5</v>
+      </c>
+      <c r="H9" s="143"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>513</v>
+        <v>592</v>
       </c>
       <c r="C10" s="54">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="108"/>
+        <v>10.5</v>
+      </c>
+      <c r="D10" s="132"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81" t="s">
+        <v>630</v>
+      </c>
+      <c r="G10" s="81">
+        <f>SUM(G7:G9)</f>
+        <v>16.8</v>
+      </c>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="143"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>513</v>
+        <v>592</v>
       </c>
       <c r="C11" s="64">
-        <v>7.6</v>
-      </c>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
+        <v>5.6</v>
+      </c>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="64" t="s">
-        <v>537</v>
-      </c>
-      <c r="B12" s="64" t="s">
-        <v>513</v>
-      </c>
-      <c r="C12" s="64">
-        <v>4.7</v>
-      </c>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
+      <c r="A12" s="54" t="s">
+        <v>545</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>592</v>
+      </c>
+      <c r="C12" s="54">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="143"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="51" t="s">
+      <c r="A13" s="64" t="s">
+        <v>582</v>
+      </c>
+      <c r="B13" s="64" t="s">
+        <v>592</v>
+      </c>
+      <c r="C13" s="64">
+        <v>15.7</v>
+      </c>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="51" t="s">
         <v>630</v>
       </c>
-      <c r="C13" s="85">
-        <f>SUM(C5:C12)</f>
-        <v>84.199999999999989</v>
-      </c>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
+      <c r="C14" s="85">
+        <f>SUM(C7:C13)</f>
+        <v>91.100000000000009</v>
+      </c>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="143"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="D4:K13"/>
+  <mergeCells count="11">
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="E11:G14"/>
+    <mergeCell ref="H6:K14"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="D6:D14"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
@@ -6372,17 +7281,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -6390,18 +7299,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="115"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -6413,18 +7322,300 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="135" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="120" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="144" t="s">
+        <v>636</v>
+      </c>
+      <c r="I3" s="154"/>
+      <c r="J3" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="72">
+        <f>C13</f>
+        <v>84.199999999999989</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="69" t="s">
+        <v>627</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>628</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>629</v>
+      </c>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="64" t="s">
+        <v>521</v>
+      </c>
+      <c r="B5" s="64" t="s">
+        <v>513</v>
+      </c>
+      <c r="C5" s="64">
+        <v>23.5</v>
+      </c>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="54" t="s">
+        <v>522</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>513</v>
+      </c>
+      <c r="C6" s="54">
+        <v>4.8</v>
+      </c>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="132"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="64" t="s">
+        <v>523</v>
+      </c>
+      <c r="B7" s="64" t="s">
+        <v>513</v>
+      </c>
+      <c r="C7" s="64">
+        <v>19.5</v>
+      </c>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="54" t="s">
+        <v>524</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>513</v>
+      </c>
+      <c r="C8" s="54">
+        <v>10.3</v>
+      </c>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="132"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="64" t="s">
+        <v>525</v>
+      </c>
+      <c r="B9" s="64" t="s">
+        <v>513</v>
+      </c>
+      <c r="C9" s="64">
+        <v>5.6</v>
+      </c>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="54" t="s">
+        <v>531</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>513</v>
+      </c>
+      <c r="C10" s="54">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="132"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="64" t="s">
+        <v>532</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>513</v>
+      </c>
+      <c r="C11" s="64">
+        <v>7.6</v>
+      </c>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
+    </row>
+    <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="64" t="s">
+        <v>537</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>513</v>
+      </c>
+      <c r="C12" s="64">
+        <v>4.7</v>
+      </c>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="51" t="s">
+        <v>630</v>
+      </c>
+      <c r="C13" s="85">
+        <f>SUM(C5:C12)</f>
+        <v>84.199999999999989</v>
+      </c>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="D4:K13"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" customWidth="1"/>
+    <col min="4" max="4" width="4.109375" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="142" t="s">
+        <v>625</v>
+      </c>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+    </row>
+    <row r="2" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
+        <v>626</v>
+      </c>
+      <c r="B2" s="133" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
+        <v>631</v>
+      </c>
+      <c r="I2" s="139"/>
+      <c r="J2" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="71" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="79">
+        <v>1</v>
+      </c>
+      <c r="B3" s="135" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="144" t="s">
         <v>637</v>
       </c>
-      <c r="I3" s="130"/>
+      <c r="I3" s="154"/>
       <c r="J3" s="79" t="s">
         <v>20</v>
       </c>
@@ -6443,14 +7634,14 @@
       <c r="C4" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="64" t="s">
@@ -6462,14 +7653,14 @@
       <c r="C5" s="64">
         <v>4.8</v>
       </c>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
@@ -6481,14 +7672,14 @@
       <c r="C6" s="54">
         <v>23.6</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="132"/>
+      <c r="K6" s="132"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="64" t="s">
@@ -6500,14 +7691,14 @@
       <c r="C7" s="64">
         <v>19.600000000000001</v>
       </c>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="54" t="s">
@@ -6519,14 +7710,14 @@
       <c r="C8" s="54">
         <v>10.5</v>
       </c>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="108"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
+      <c r="K8" s="132"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64" t="s">
@@ -6538,14 +7729,14 @@
       <c r="C9" s="64">
         <v>5.6</v>
       </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="108"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="54" t="s">
@@ -6557,14 +7748,14 @@
       <c r="C10" s="54">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="108"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="132"/>
     </row>
     <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="64" t="s">
@@ -6576,14 +7767,14 @@
       <c r="C11" s="64">
         <v>7.6</v>
       </c>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
@@ -6595,14 +7786,14 @@
       <c r="C12" s="54">
         <v>4.5</v>
       </c>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="51" t="s">
@@ -6612,14 +7803,14 @@
         <f>SUM(C5:C12)</f>
         <v>84.399999999999991</v>
       </c>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6636,6 +7827,149 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="130" t="s">
+        <v>625</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+    </row>
+    <row r="2" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
+        <v>626</v>
+      </c>
+      <c r="B2" s="133" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="134"/>
+      <c r="D2" s="99" t="s">
+        <v>631</v>
+      </c>
+      <c r="E2" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="101" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="98">
+        <v>1</v>
+      </c>
+      <c r="B3" s="135" t="s">
+        <v>676</v>
+      </c>
+      <c r="C3" s="136"/>
+      <c r="D3" s="100" t="s">
+        <v>675</v>
+      </c>
+      <c r="E3" s="98" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="105">
+        <f>B9</f>
+        <v>9482.4000000000015</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="137"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+    </row>
+    <row r="5" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="69" t="s">
+        <v>674</v>
+      </c>
+      <c r="B5" s="69" t="s">
+        <v>629</v>
+      </c>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="64">
+        <v>1</v>
+      </c>
+      <c r="B6" s="103">
+        <f>1581.9+140.9</f>
+        <v>1722.8000000000002</v>
+      </c>
+      <c r="C6" s="132"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="54">
+        <v>2</v>
+      </c>
+      <c r="B7" s="104">
+        <v>4179.3</v>
+      </c>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="64">
+        <v>3</v>
+      </c>
+      <c r="B8" s="103">
+        <v>3580.3</v>
+      </c>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+    </row>
+    <row r="9" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="102" t="s">
+        <v>630</v>
+      </c>
+      <c r="B9" s="85">
+        <f>SUM(B6:B8)</f>
+        <v>9482.4000000000015</v>
+      </c>
+      <c r="C9" s="132"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C5:F9"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6654,17 +7988,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -6672,18 +8006,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="115"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -6695,18 +8029,18 @@
       <c r="A3" s="97">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="135" t="s">
         <v>645</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="120" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="144" t="s">
         <v>646</v>
       </c>
-      <c r="I3" s="121"/>
+      <c r="I3" s="145"/>
       <c r="J3" s="97" t="s">
         <v>20</v>
       </c>
@@ -6716,17 +8050,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="113"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
+      <c r="A4" s="137"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
     </row>
     <row r="5" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
@@ -6738,7 +8072,7 @@
       <c r="C5" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="D5" s="108"/>
+      <c r="D5" s="132"/>
       <c r="E5" s="69" t="s">
         <v>647</v>
       </c>
@@ -6748,7 +8082,7 @@
       <c r="G5" s="69" t="s">
         <v>629</v>
       </c>
-      <c r="H5" s="108"/>
+      <c r="H5" s="132"/>
       <c r="I5" s="69" t="s">
         <v>647</v>
       </c>
@@ -6769,7 +8103,7 @@
       <c r="C6" s="64">
         <v>25.1</v>
       </c>
-      <c r="D6" s="108"/>
+      <c r="D6" s="132"/>
       <c r="E6" s="64">
         <v>27</v>
       </c>
@@ -6779,7 +8113,7 @@
       <c r="G6" s="64">
         <v>13.4</v>
       </c>
-      <c r="H6" s="108"/>
+      <c r="H6" s="132"/>
       <c r="I6" s="64">
         <v>57</v>
       </c>
@@ -6800,7 +8134,7 @@
       <c r="C7" s="54">
         <v>12.5</v>
       </c>
-      <c r="D7" s="108"/>
+      <c r="D7" s="132"/>
       <c r="E7" s="54">
         <v>28</v>
       </c>
@@ -6810,7 +8144,7 @@
       <c r="G7" s="54">
         <v>10.26</v>
       </c>
-      <c r="H7" s="108"/>
+      <c r="H7" s="132"/>
       <c r="I7" s="54">
         <v>58</v>
       </c>
@@ -6831,7 +8165,7 @@
       <c r="C8" s="64">
         <v>5.4</v>
       </c>
-      <c r="D8" s="108"/>
+      <c r="D8" s="132"/>
       <c r="E8" s="64">
         <v>29</v>
       </c>
@@ -6841,7 +8175,7 @@
       <c r="G8" s="64">
         <v>23.4</v>
       </c>
-      <c r="H8" s="108"/>
+      <c r="H8" s="132"/>
       <c r="I8" s="64">
         <v>59</v>
       </c>
@@ -6862,7 +8196,7 @@
       <c r="C9" s="54">
         <v>21</v>
       </c>
-      <c r="D9" s="108"/>
+      <c r="D9" s="132"/>
       <c r="E9" s="54">
         <v>30</v>
       </c>
@@ -6872,7 +8206,7 @@
       <c r="G9" s="54">
         <v>4.67</v>
       </c>
-      <c r="H9" s="108"/>
+      <c r="H9" s="132"/>
       <c r="I9" s="54">
         <v>60</v>
       </c>
@@ -6893,7 +8227,7 @@
       <c r="C10" s="64">
         <v>5.8</v>
       </c>
-      <c r="D10" s="108"/>
+      <c r="D10" s="132"/>
       <c r="E10" s="64">
         <v>31</v>
       </c>
@@ -6903,7 +8237,7 @@
       <c r="G10" s="64">
         <v>19.239999999999998</v>
       </c>
-      <c r="H10" s="108"/>
+      <c r="H10" s="132"/>
       <c r="I10" s="64">
         <v>61</v>
       </c>
@@ -6924,7 +8258,7 @@
       <c r="C11" s="54">
         <v>32.200000000000003</v>
       </c>
-      <c r="D11" s="108"/>
+      <c r="D11" s="132"/>
       <c r="E11" s="54">
         <v>32</v>
       </c>
@@ -6934,7 +8268,7 @@
       <c r="G11" s="54">
         <v>19.829999999999998</v>
       </c>
-      <c r="H11" s="108"/>
+      <c r="H11" s="132"/>
       <c r="I11" s="54">
         <v>62</v>
       </c>
@@ -6955,7 +8289,7 @@
       <c r="C12" s="64">
         <v>12.2</v>
       </c>
-      <c r="D12" s="108"/>
+      <c r="D12" s="132"/>
       <c r="E12" s="64">
         <v>33</v>
       </c>
@@ -6965,7 +8299,7 @@
       <c r="G12" s="64">
         <v>10.25</v>
       </c>
-      <c r="H12" s="108"/>
+      <c r="H12" s="132"/>
       <c r="I12" s="64">
         <v>63</v>
       </c>
@@ -6986,7 +8320,7 @@
       <c r="C13" s="54">
         <v>7.5</v>
       </c>
-      <c r="D13" s="108"/>
+      <c r="D13" s="132"/>
       <c r="E13" s="54">
         <v>34</v>
       </c>
@@ -6996,7 +8330,7 @@
       <c r="G13" s="54">
         <v>5.44</v>
       </c>
-      <c r="H13" s="108"/>
+      <c r="H13" s="132"/>
       <c r="I13" s="54">
         <v>64</v>
       </c>
@@ -7017,7 +8351,7 @@
       <c r="C14" s="64">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D14" s="108"/>
+      <c r="D14" s="132"/>
       <c r="E14" s="64">
         <v>35</v>
       </c>
@@ -7027,7 +8361,7 @@
       <c r="G14" s="64">
         <v>4.55</v>
       </c>
-      <c r="H14" s="108"/>
+      <c r="H14" s="132"/>
       <c r="I14" s="64">
         <v>65</v>
       </c>
@@ -7048,7 +8382,7 @@
       <c r="C15" s="54">
         <v>8.9</v>
       </c>
-      <c r="D15" s="108"/>
+      <c r="D15" s="132"/>
       <c r="E15" s="54">
         <v>36</v>
       </c>
@@ -7058,7 +8392,7 @@
       <c r="G15" s="54">
         <v>15.17</v>
       </c>
-      <c r="H15" s="108"/>
+      <c r="H15" s="132"/>
       <c r="I15" s="54">
         <v>66</v>
       </c>
@@ -7079,7 +8413,7 @@
       <c r="C16" s="64">
         <v>15.2</v>
       </c>
-      <c r="D16" s="108"/>
+      <c r="D16" s="132"/>
       <c r="E16" s="64">
         <v>37</v>
       </c>
@@ -7089,7 +8423,7 @@
       <c r="G16" s="64">
         <v>10.79</v>
       </c>
-      <c r="H16" s="108"/>
+      <c r="H16" s="132"/>
       <c r="I16" s="64">
         <v>67</v>
       </c>
@@ -7110,7 +8444,7 @@
       <c r="C17" s="54">
         <v>14</v>
       </c>
-      <c r="D17" s="108"/>
+      <c r="D17" s="132"/>
       <c r="E17" s="54">
         <v>38</v>
       </c>
@@ -7120,7 +8454,7 @@
       <c r="G17" s="54">
         <v>10.34</v>
       </c>
-      <c r="H17" s="108"/>
+      <c r="H17" s="132"/>
       <c r="I17" s="54">
         <v>68</v>
       </c>
@@ -7141,7 +8475,7 @@
       <c r="C18" s="64">
         <v>12.1</v>
       </c>
-      <c r="D18" s="108"/>
+      <c r="D18" s="132"/>
       <c r="E18" s="64">
         <v>39</v>
       </c>
@@ -7151,7 +8485,7 @@
       <c r="G18" s="64">
         <v>7.99</v>
       </c>
-      <c r="H18" s="108"/>
+      <c r="H18" s="132"/>
       <c r="I18" s="64">
         <v>69</v>
       </c>
@@ -7172,7 +8506,7 @@
       <c r="C19" s="54">
         <v>15.28</v>
       </c>
-      <c r="D19" s="108"/>
+      <c r="D19" s="132"/>
       <c r="E19" s="54">
         <v>40</v>
       </c>
@@ -7182,7 +8516,7 @@
       <c r="G19" s="54">
         <v>7.6</v>
       </c>
-      <c r="H19" s="108"/>
+      <c r="H19" s="132"/>
       <c r="I19" s="54">
         <v>70</v>
       </c>
@@ -7203,7 +8537,7 @@
       <c r="C20" s="64">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D20" s="108"/>
+      <c r="D20" s="132"/>
       <c r="E20" s="64">
         <v>41</v>
       </c>
@@ -7213,7 +8547,7 @@
       <c r="G20" s="64">
         <v>10.37</v>
       </c>
-      <c r="H20" s="108"/>
+      <c r="H20" s="132"/>
       <c r="I20" s="64">
         <v>71</v>
       </c>
@@ -7234,7 +8568,7 @@
       <c r="C21" s="54">
         <v>7.7</v>
       </c>
-      <c r="D21" s="108"/>
+      <c r="D21" s="132"/>
       <c r="E21" s="54">
         <v>42</v>
       </c>
@@ -7244,7 +8578,7 @@
       <c r="G21" s="54">
         <v>16.13</v>
       </c>
-      <c r="H21" s="108"/>
+      <c r="H21" s="132"/>
       <c r="I21" s="54">
         <v>72</v>
       </c>
@@ -7265,7 +8599,7 @@
       <c r="C22" s="64">
         <v>14.6</v>
       </c>
-      <c r="D22" s="108"/>
+      <c r="D22" s="132"/>
       <c r="E22" s="64">
         <v>43</v>
       </c>
@@ -7275,7 +8609,7 @@
       <c r="G22" s="64">
         <v>22.18</v>
       </c>
-      <c r="H22" s="108"/>
+      <c r="H22" s="132"/>
       <c r="I22" s="64">
         <v>73</v>
       </c>
@@ -7296,7 +8630,7 @@
       <c r="C23" s="54">
         <v>12.7</v>
       </c>
-      <c r="D23" s="108"/>
+      <c r="D23" s="132"/>
       <c r="E23" s="54">
         <v>44</v>
       </c>
@@ -7306,7 +8640,7 @@
       <c r="G23" s="54">
         <v>4.37</v>
       </c>
-      <c r="H23" s="108"/>
+      <c r="H23" s="132"/>
       <c r="I23" s="54">
         <v>74</v>
       </c>
@@ -7327,7 +8661,7 @@
       <c r="C24" s="64">
         <v>37</v>
       </c>
-      <c r="D24" s="108"/>
+      <c r="D24" s="132"/>
       <c r="E24" s="64">
         <v>45</v>
       </c>
@@ -7337,7 +8671,7 @@
       <c r="G24" s="64">
         <v>5.64</v>
       </c>
-      <c r="H24" s="108"/>
+      <c r="H24" s="132"/>
       <c r="I24" s="64">
         <v>75</v>
       </c>
@@ -7358,7 +8692,7 @@
       <c r="C25" s="54">
         <v>7.4</v>
       </c>
-      <c r="D25" s="108"/>
+      <c r="D25" s="132"/>
       <c r="E25" s="54">
         <v>46</v>
       </c>
@@ -7368,7 +8702,7 @@
       <c r="G25" s="54">
         <v>25.37</v>
       </c>
-      <c r="H25" s="108"/>
+      <c r="H25" s="132"/>
       <c r="I25" s="54">
         <v>76</v>
       </c>
@@ -7389,7 +8723,7 @@
       <c r="C26" s="64">
         <v>117.2</v>
       </c>
-      <c r="D26" s="108"/>
+      <c r="D26" s="132"/>
       <c r="E26" s="64">
         <v>47</v>
       </c>
@@ -7399,7 +8733,7 @@
       <c r="G26" s="64">
         <v>5.64</v>
       </c>
-      <c r="H26" s="108"/>
+      <c r="H26" s="132"/>
       <c r="I26" s="64">
         <v>77</v>
       </c>
@@ -7420,7 +8754,7 @@
       <c r="C27" s="54">
         <v>20.7</v>
       </c>
-      <c r="D27" s="108"/>
+      <c r="D27" s="132"/>
       <c r="E27" s="54">
         <v>48</v>
       </c>
@@ -7430,7 +8764,7 @@
       <c r="G27" s="54">
         <v>25.37</v>
       </c>
-      <c r="H27" s="108"/>
+      <c r="H27" s="132"/>
       <c r="I27" s="54">
         <v>78</v>
       </c>
@@ -7451,7 +8785,7 @@
       <c r="C28" s="64">
         <v>37.4</v>
       </c>
-      <c r="D28" s="108"/>
+      <c r="D28" s="132"/>
       <c r="E28" s="64">
         <v>49</v>
       </c>
@@ -7461,7 +8795,7 @@
       <c r="G28" s="64">
         <v>9.07</v>
       </c>
-      <c r="H28" s="108"/>
+      <c r="H28" s="132"/>
       <c r="I28" s="64">
         <v>79</v>
       </c>
@@ -7482,7 +8816,7 @@
       <c r="C29" s="54">
         <v>13.1</v>
       </c>
-      <c r="D29" s="108"/>
+      <c r="D29" s="132"/>
       <c r="E29" s="54">
         <v>50</v>
       </c>
@@ -7492,7 +8826,7 @@
       <c r="G29" s="54">
         <v>16.559999999999999</v>
       </c>
-      <c r="H29" s="108"/>
+      <c r="H29" s="132"/>
       <c r="J29" s="51" t="s">
         <v>630</v>
       </c>
@@ -7511,7 +8845,7 @@
       <c r="C30" s="64">
         <v>16.899999999999999</v>
       </c>
-      <c r="D30" s="108"/>
+      <c r="D30" s="132"/>
       <c r="E30" s="64">
         <v>51</v>
       </c>
@@ -7521,10 +8855,10 @@
       <c r="G30" s="64">
         <v>8.1199999999999992</v>
       </c>
-      <c r="H30" s="108"/>
-      <c r="I30" s="108"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="108"/>
+      <c r="H30" s="132"/>
+      <c r="I30" s="132"/>
+      <c r="J30" s="132"/>
+      <c r="K30" s="132"/>
     </row>
     <row r="31" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="54">
@@ -7536,7 +8870,7 @@
       <c r="C31" s="54">
         <v>104</v>
       </c>
-      <c r="D31" s="108"/>
+      <c r="D31" s="132"/>
       <c r="E31" s="54">
         <v>52</v>
       </c>
@@ -7546,10 +8880,10 @@
       <c r="G31" s="54">
         <v>8.89</v>
       </c>
-      <c r="H31" s="108"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="108"/>
-      <c r="K31" s="108"/>
+      <c r="H31" s="132"/>
+      <c r="I31" s="132"/>
+      <c r="J31" s="132"/>
+      <c r="K31" s="132"/>
     </row>
     <row r="32" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="51" t="s">
@@ -7559,7 +8893,7 @@
         <f>SUM(C6:C31)</f>
         <v>592.27999999999986</v>
       </c>
-      <c r="D32" s="108"/>
+      <c r="D32" s="132"/>
       <c r="E32" s="64">
         <v>53</v>
       </c>
@@ -7569,16 +8903,16 @@
       <c r="G32" s="64">
         <v>9.69</v>
       </c>
-      <c r="H32" s="108"/>
-      <c r="I32" s="108"/>
-      <c r="J32" s="108"/>
-      <c r="K32" s="108"/>
+      <c r="H32" s="132"/>
+      <c r="I32" s="132"/>
+      <c r="J32" s="132"/>
+      <c r="K32" s="132"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="119"/>
-      <c r="B33" s="119"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="108"/>
+      <c r="A33" s="143"/>
+      <c r="B33" s="143"/>
+      <c r="C33" s="143"/>
+      <c r="D33" s="132"/>
       <c r="E33" s="54">
         <v>54</v>
       </c>
@@ -7588,16 +8922,16 @@
       <c r="G33" s="54">
         <v>4.1900000000000004</v>
       </c>
-      <c r="H33" s="108"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="108"/>
-      <c r="K33" s="108"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="132"/>
+      <c r="K33" s="132"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="119"/>
-      <c r="B34" s="119"/>
-      <c r="C34" s="119"/>
-      <c r="D34" s="108"/>
+      <c r="A34" s="143"/>
+      <c r="B34" s="143"/>
+      <c r="C34" s="143"/>
+      <c r="D34" s="132"/>
       <c r="E34" s="64">
         <v>55</v>
       </c>
@@ -7607,16 +8941,16 @@
       <c r="G34" s="64">
         <v>19.78</v>
       </c>
-      <c r="H34" s="108"/>
-      <c r="I34" s="108"/>
-      <c r="J34" s="108"/>
-      <c r="K34" s="108"/>
+      <c r="H34" s="132"/>
+      <c r="I34" s="132"/>
+      <c r="J34" s="132"/>
+      <c r="K34" s="132"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="119"/>
-      <c r="B35" s="119"/>
-      <c r="C35" s="119"/>
-      <c r="D35" s="108"/>
+      <c r="A35" s="143"/>
+      <c r="B35" s="143"/>
+      <c r="C35" s="143"/>
+      <c r="D35" s="132"/>
       <c r="E35" s="54">
         <v>56</v>
       </c>
@@ -7626,16 +8960,16 @@
       <c r="G35" s="54">
         <v>8.25</v>
       </c>
-      <c r="H35" s="108"/>
-      <c r="I35" s="108"/>
-      <c r="J35" s="108"/>
-      <c r="K35" s="108"/>
+      <c r="H35" s="132"/>
+      <c r="I35" s="132"/>
+      <c r="J35" s="132"/>
+      <c r="K35" s="132"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="119"/>
-      <c r="B36" s="119"/>
-      <c r="C36" s="119"/>
-      <c r="D36" s="108"/>
+      <c r="A36" s="143"/>
+      <c r="B36" s="143"/>
+      <c r="C36" s="143"/>
+      <c r="D36" s="132"/>
       <c r="F36" s="51" t="s">
         <v>630</v>
       </c>
@@ -7643,10 +8977,10 @@
         <f>SUM(G6:G35)</f>
         <v>362.54999999999995</v>
       </c>
-      <c r="H36" s="108"/>
-      <c r="I36" s="108"/>
-      <c r="J36" s="108"/>
-      <c r="K36" s="108"/>
+      <c r="H36" s="132"/>
+      <c r="I36" s="132"/>
+      <c r="J36" s="132"/>
+      <c r="K36" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7666,7 +9000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7682,14 +9016,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
       <c r="G1" s="70"/>
       <c r="H1" s="70"/>
     </row>
@@ -7697,15 +9031,15 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="125" t="s">
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="149" t="s">
         <v>631</v>
       </c>
-      <c r="F2" s="125"/>
+      <c r="F2" s="149"/>
       <c r="G2" s="67" t="s">
         <v>5</v>
       </c>
@@ -7717,15 +9051,15 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="124" t="s">
+      <c r="B3" s="148" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="126" t="s">
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="150" t="s">
         <v>192</v>
       </c>
-      <c r="F3" s="126"/>
+      <c r="F3" s="150"/>
       <c r="G3" s="79" t="s">
         <v>20</v>
       </c>
@@ -7735,14 +9069,14 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="108"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
+      <c r="A4" s="132"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="132"/>
     </row>
     <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
@@ -7760,9 +9094,9 @@
       <c r="E5" s="69" t="s">
         <v>641</v>
       </c>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="84" t="s">
@@ -7781,9 +9115,9 @@
         <f>C6*D6</f>
         <v>6.9375</v>
       </c>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
+      <c r="F6" s="143"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="83" t="s">
@@ -7802,9 +9136,9 @@
         <f>C7*D7</f>
         <v>9.84</v>
       </c>
-      <c r="F7" s="119"/>
-      <c r="G7" s="119"/>
-      <c r="H7" s="119"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="84" t="s">
@@ -7823,9 +9157,9 @@
         <f t="shared" ref="E8:E11" si="0">C8*D8</f>
         <v>1.425</v>
       </c>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="83" t="s">
@@ -7844,9 +9178,9 @@
         <f t="shared" si="0"/>
         <v>1.395</v>
       </c>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
+      <c r="F9" s="143"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="84" t="s">
@@ -7865,9 +9199,9 @@
         <f t="shared" si="0"/>
         <v>1.5450000000000002</v>
       </c>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="83" t="s">
@@ -7886,9 +9220,9 @@
         <f t="shared" si="0"/>
         <v>1.38</v>
       </c>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="84" t="s">
@@ -7907,14 +9241,14 @@
         <f t="shared" ref="E12" si="1">C12*D12</f>
         <v>1.38</v>
       </c>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="119"/>
+      <c r="F12" s="143"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="122"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
+      <c r="A13" s="146"/>
+      <c r="B13" s="146"/>
+      <c r="C13" s="146"/>
       <c r="D13" t="s">
         <v>642</v>
       </c>
@@ -7922,9 +9256,9 @@
         <f>SUM(E6:E12)</f>
         <v>23.9025</v>
       </c>
-      <c r="F13" s="119"/>
-      <c r="G13" s="119"/>
-      <c r="H13" s="119"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7941,7 +9275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7960,17 +9294,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -7978,18 +9312,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="115"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -8001,18 +9335,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="135" t="s">
         <v>413</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="127" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="151" t="s">
         <v>644</v>
       </c>
-      <c r="I3" s="128"/>
+      <c r="I3" s="152"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -8025,18 +9359,18 @@
       <c r="A4" s="89">
         <v>2</v>
       </c>
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="135" t="s">
         <v>387</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="127" t="s">
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="151" t="s">
         <v>643</v>
       </c>
-      <c r="I4" s="128"/>
+      <c r="I4" s="152"/>
       <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
@@ -8535,17 +9869,17 @@
       <c r="K28" s="95"/>
     </row>
     <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="118" t="s">
+      <c r="A31" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B31" s="118"/>
-      <c r="C31" s="118"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="118"/>
+      <c r="B31" s="142"/>
+      <c r="C31" s="142"/>
+      <c r="D31" s="142"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="142"/>
+      <c r="I31" s="142"/>
       <c r="J31" s="70"/>
       <c r="K31" s="70"/>
     </row>
@@ -8553,18 +9887,18 @@
       <c r="A32" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B32" s="109" t="s">
+      <c r="B32" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="110"/>
-      <c r="H32" s="114" t="s">
+      <c r="C32" s="141"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="134"/>
+      <c r="H32" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I32" s="115"/>
+      <c r="I32" s="139"/>
       <c r="J32" s="67" t="s">
         <v>5</v>
       </c>
@@ -8576,18 +9910,18 @@
       <c r="A33" s="89">
         <v>1</v>
       </c>
-      <c r="B33" s="111" t="s">
+      <c r="B33" s="135" t="s">
         <v>413</v>
       </c>
-      <c r="C33" s="116"/>
-      <c r="D33" s="116"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="112"/>
-      <c r="H33" s="127" t="s">
+      <c r="C33" s="140"/>
+      <c r="D33" s="140"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="140"/>
+      <c r="G33" s="136"/>
+      <c r="H33" s="151" t="s">
         <v>632</v>
       </c>
-      <c r="I33" s="128"/>
+      <c r="I33" s="152"/>
       <c r="J33" s="89" t="s">
         <v>20</v>
       </c>
@@ -8600,18 +9934,18 @@
       <c r="A34" s="89">
         <v>2</v>
       </c>
-      <c r="B34" s="111" t="s">
+      <c r="B34" s="135" t="s">
         <v>387</v>
       </c>
-      <c r="C34" s="116"/>
-      <c r="D34" s="116"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="112"/>
-      <c r="H34" s="127" t="s">
+      <c r="C34" s="140"/>
+      <c r="D34" s="140"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="136"/>
+      <c r="H34" s="151" t="s">
         <v>633</v>
       </c>
-      <c r="I34" s="128"/>
+      <c r="I34" s="152"/>
       <c r="J34" s="89" t="s">
         <v>20</v>
       </c>
@@ -9181,23 +10515,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -9205,18 +10539,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="115"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -9228,18 +10562,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="129" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="153" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="128"/>
+      <c r="I3" s="152"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -9997,36 +11331,36 @@
       <c r="K41" s="81"/>
     </row>
     <row r="43" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="106" t="s">
+      <c r="A43" s="130" t="s">
         <v>625</v>
       </c>
-      <c r="B43" s="107"/>
-      <c r="C43" s="107"/>
-      <c r="D43" s="107"/>
-      <c r="E43" s="107"/>
-      <c r="F43" s="107"/>
-      <c r="G43" s="107"/>
-      <c r="H43" s="107"/>
-      <c r="I43" s="107"/>
-      <c r="J43" s="107"/>
-      <c r="K43" s="107"/>
+      <c r="B43" s="131"/>
+      <c r="C43" s="131"/>
+      <c r="D43" s="131"/>
+      <c r="E43" s="131"/>
+      <c r="F43" s="131"/>
+      <c r="G43" s="131"/>
+      <c r="H43" s="131"/>
+      <c r="I43" s="131"/>
+      <c r="J43" s="131"/>
+      <c r="K43" s="131"/>
     </row>
     <row r="44" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B44" s="109" t="s">
+      <c r="B44" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="117"/>
-      <c r="D44" s="117"/>
-      <c r="E44" s="117"/>
-      <c r="F44" s="117"/>
-      <c r="G44" s="110"/>
-      <c r="H44" s="114" t="s">
+      <c r="C44" s="141"/>
+      <c r="D44" s="141"/>
+      <c r="E44" s="141"/>
+      <c r="F44" s="141"/>
+      <c r="G44" s="134"/>
+      <c r="H44" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I44" s="115"/>
+      <c r="I44" s="139"/>
       <c r="J44" s="67" t="s">
         <v>5</v>
       </c>
@@ -10038,18 +11372,18 @@
       <c r="A45" s="89">
         <v>1</v>
       </c>
-      <c r="B45" s="111" t="s">
+      <c r="B45" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="116"/>
-      <c r="D45" s="116"/>
-      <c r="E45" s="116"/>
-      <c r="F45" s="116"/>
-      <c r="G45" s="112"/>
-      <c r="H45" s="129" t="s">
+      <c r="C45" s="140"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="136"/>
+      <c r="H45" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="I45" s="128"/>
+      <c r="I45" s="152"/>
       <c r="J45" s="89" t="s">
         <v>20</v>
       </c>
@@ -10565,22 +11899,22 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="B45:G45"/>
     <mergeCell ref="H45:I45"/>
     <mergeCell ref="A43:K43"/>
     <mergeCell ref="B44:G44"/>
     <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10599,17 +11933,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
       <c r="J1" s="70"/>
       <c r="K1" s="70"/>
     </row>
@@ -10617,18 +11951,18 @@
       <c r="A2" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="114" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I2" s="115"/>
+      <c r="I2" s="139"/>
       <c r="J2" s="67" t="s">
         <v>5</v>
       </c>
@@ -10640,18 +11974,18 @@
       <c r="A3" s="89">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="135" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="120" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="144" t="s">
         <v>636</v>
       </c>
-      <c r="I3" s="130"/>
+      <c r="I3" s="154"/>
       <c r="J3" s="89" t="s">
         <v>20</v>
       </c>
@@ -10664,18 +11998,18 @@
       <c r="A4" s="89">
         <v>2</v>
       </c>
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="120" t="s">
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="144" t="s">
         <v>623</v>
       </c>
-      <c r="I4" s="130"/>
+      <c r="I4" s="154"/>
       <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
@@ -11124,17 +12458,17 @@
       <c r="K26" s="95"/>
     </row>
     <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="118" t="s">
+      <c r="A28" s="142" t="s">
         <v>625</v>
       </c>
-      <c r="B28" s="118"/>
-      <c r="C28" s="118"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="118"/>
+      <c r="B28" s="142"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="142"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="142"/>
       <c r="J28" s="70"/>
       <c r="K28" s="70"/>
     </row>
@@ -11142,18 +12476,18 @@
       <c r="A29" s="66" t="s">
         <v>626</v>
       </c>
-      <c r="B29" s="109" t="s">
+      <c r="B29" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="117"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="117"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="114" t="s">
+      <c r="C29" s="141"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="134"/>
+      <c r="H29" s="138" t="s">
         <v>631</v>
       </c>
-      <c r="I29" s="115"/>
+      <c r="I29" s="139"/>
       <c r="J29" s="67" t="s">
         <v>5</v>
       </c>
@@ -11165,18 +12499,18 @@
       <c r="A30" s="89">
         <v>1</v>
       </c>
-      <c r="B30" s="111" t="s">
+      <c r="B30" s="135" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="116"/>
-      <c r="D30" s="116"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="116"/>
-      <c r="G30" s="112"/>
-      <c r="H30" s="120" t="s">
+      <c r="C30" s="140"/>
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="144" t="s">
         <v>637</v>
       </c>
-      <c r="I30" s="130"/>
+      <c r="I30" s="154"/>
       <c r="J30" s="89" t="s">
         <v>20</v>
       </c>
@@ -11189,18 +12523,18 @@
       <c r="A31" s="89">
         <v>2</v>
       </c>
-      <c r="B31" s="111" t="s">
+      <c r="B31" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="116"/>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="120" t="s">
+      <c r="C31" s="140"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="136"/>
+      <c r="H31" s="144" t="s">
         <v>622</v>
       </c>
-      <c r="I31" s="130"/>
+      <c r="I31" s="154"/>
       <c r="J31" s="89" t="s">
         <v>20</v>
       </c>
@@ -11607,7 +12941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -16616,7 +17950,7 @@
       <c r="S148" s="10"/>
       <c r="T148" s="10"/>
     </row>
-    <row r="149" spans="1:20" ht="36" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:20" ht="18" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>239</v>
       </c>
@@ -20250,7 +21584,7 @@
       <c r="S255" s="10"/>
       <c r="T255" s="10"/>
     </row>
-    <row r="256" spans="1:20" ht="54" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:20" ht="72" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>418</v>
       </c>
@@ -20384,7 +21718,7 @@
       <c r="S259" s="10"/>
       <c r="T259" s="10"/>
     </row>
-    <row r="260" spans="1:20" ht="54" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:20" ht="72" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>425</v>
       </c>
@@ -20590,7 +21924,7 @@
       <c r="S265" s="10"/>
       <c r="T265" s="10"/>
     </row>
-    <row r="266" spans="1:20" ht="54" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:20" ht="72" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>431</v>
       </c>
@@ -20730,7 +22064,7 @@
       <c r="S269" s="10"/>
       <c r="T269" s="10"/>
     </row>
-    <row r="270" spans="1:20" ht="54" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:20" ht="72" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>435</v>
       </c>
@@ -20836,7 +22170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -24075,840 +25409,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="4" max="4" width="9.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
-        <v>605</v>
-      </c>
-      <c r="B1" s="73" t="s">
-        <v>583</v>
-      </c>
-      <c r="C1" s="73" t="s">
-        <v>604</v>
-      </c>
-      <c r="D1" s="73" t="s">
-        <v>584</v>
-      </c>
-      <c r="E1" s="73" t="s">
-        <v>593</v>
-      </c>
-      <c r="F1" s="73" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="64">
-        <v>2</v>
-      </c>
-      <c r="B2" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C2" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D2" s="64" t="s">
-        <v>442</v>
-      </c>
-      <c r="E2" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F2" s="64">
-        <v>80.599999999999994</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54">
-        <v>2</v>
-      </c>
-      <c r="B3" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D3" s="54" t="s">
-        <v>443</v>
-      </c>
-      <c r="E3" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F3" s="54">
-        <v>64.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="64">
-        <v>2</v>
-      </c>
-      <c r="B4" s="64" t="s">
-        <v>607</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>444</v>
-      </c>
-      <c r="E4" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F4" s="64">
-        <v>218.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54">
-        <v>2</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D5" s="54" t="s">
-        <v>445</v>
-      </c>
-      <c r="E5" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F5" s="54">
-        <v>45.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="64">
-        <v>2</v>
-      </c>
-      <c r="B6" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C6" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D6" s="64" t="s">
-        <v>446</v>
-      </c>
-      <c r="E6" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F6" s="64">
-        <v>18.899999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="54">
-        <v>2</v>
-      </c>
-      <c r="B7" s="54" t="s">
-        <v>617</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>558</v>
-      </c>
-      <c r="D7" s="54" t="s">
-        <v>557</v>
-      </c>
-      <c r="E7" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F7" s="54">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="64">
-        <v>2</v>
-      </c>
-      <c r="B8" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C8" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D8" s="64" t="s">
-        <v>447</v>
-      </c>
-      <c r="E8" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F8" s="64">
-        <v>63.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="54">
-        <v>2</v>
-      </c>
-      <c r="B9" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D9" s="54" t="s">
-        <v>448</v>
-      </c>
-      <c r="E9" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F9" s="54">
-        <v>64.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="64">
-        <v>2</v>
-      </c>
-      <c r="B10" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C10" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D10" s="64" t="s">
-        <v>449</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F10" s="64">
-        <v>64.900000000000006</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="54">
-        <v>2</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C11" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D11" s="54" t="s">
-        <v>450</v>
-      </c>
-      <c r="E11" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F11" s="54">
-        <v>63.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="64">
-        <v>2</v>
-      </c>
-      <c r="B12" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C12" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>451</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F12" s="64">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54">
-        <v>2</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>607</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D13" s="54" t="s">
-        <v>452</v>
-      </c>
-      <c r="E13" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F13" s="54">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="64">
-        <v>2</v>
-      </c>
-      <c r="B14" s="64" t="s">
-        <v>613</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D14" s="64" t="s">
-        <v>453</v>
-      </c>
-      <c r="E14" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F14" s="64">
-        <v>478.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54">
-        <v>2</v>
-      </c>
-      <c r="B15" s="54" t="s">
-        <v>607</v>
-      </c>
-      <c r="C15" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D15" s="54" t="s">
-        <v>454</v>
-      </c>
-      <c r="E15" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F15" s="54">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="64">
-        <v>2</v>
-      </c>
-      <c r="B16" s="64" t="s">
-        <v>607</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D16" s="64" t="s">
-        <v>455</v>
-      </c>
-      <c r="E16" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F16" s="64">
-        <v>42.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54">
-        <v>2</v>
-      </c>
-      <c r="B17" s="54" t="s">
-        <v>607</v>
-      </c>
-      <c r="C17" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D17" s="54" t="s">
-        <v>456</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F17" s="54">
-        <v>10.199999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="64">
-        <v>2</v>
-      </c>
-      <c r="B18" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C18" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D18" s="64" t="s">
-        <v>457</v>
-      </c>
-      <c r="E18" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F18" s="64">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="54">
-        <v>2</v>
-      </c>
-      <c r="B19" s="54" t="s">
-        <v>618</v>
-      </c>
-      <c r="C19" s="54" t="s">
-        <v>512</v>
-      </c>
-      <c r="D19" s="54" t="s">
-        <v>517</v>
-      </c>
-      <c r="E19" s="54" t="s">
-        <v>598</v>
-      </c>
-      <c r="F19" s="54">
-        <v>543.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="64">
-        <v>2</v>
-      </c>
-      <c r="B20" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>512</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>518</v>
-      </c>
-      <c r="E20" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F20" s="64">
-        <v>66.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="54">
-        <v>2</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C21" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D21" s="54" t="s">
-        <v>458</v>
-      </c>
-      <c r="E21" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F21" s="54">
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="64">
-        <v>2</v>
-      </c>
-      <c r="B22" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D22" s="64" t="s">
-        <v>459</v>
-      </c>
-      <c r="E22" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F22" s="64">
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="54">
-        <v>2</v>
-      </c>
-      <c r="B23" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D23" s="54" t="s">
-        <v>460</v>
-      </c>
-      <c r="E23" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F23" s="54">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="64">
-        <v>2</v>
-      </c>
-      <c r="B24" s="64" t="s">
-        <v>607</v>
-      </c>
-      <c r="C24" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D24" s="64" t="s">
-        <v>461</v>
-      </c>
-      <c r="E24" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F24" s="64">
-        <v>100.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="54">
-        <v>2</v>
-      </c>
-      <c r="B25" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D25" s="54" t="s">
-        <v>462</v>
-      </c>
-      <c r="E25" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F25" s="52">
-        <v>218.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="64">
-        <v>2</v>
-      </c>
-      <c r="B26" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C26" s="64" t="s">
-        <v>514</v>
-      </c>
-      <c r="D26" s="64" t="s">
-        <v>462</v>
-      </c>
-      <c r="E26" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F26" s="64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="54">
-        <v>2</v>
-      </c>
-      <c r="B27" s="54" t="s">
-        <v>607</v>
-      </c>
-      <c r="C27" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D27" s="54" t="s">
-        <v>463</v>
-      </c>
-      <c r="E27" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F27" s="54">
-        <v>162.9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="64">
-        <v>2</v>
-      </c>
-      <c r="B28" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C28" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D28" s="64" t="s">
-        <v>464</v>
-      </c>
-      <c r="E28" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F28" s="64">
-        <v>41.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="54">
-        <v>2</v>
-      </c>
-      <c r="B29" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D29" s="54" t="s">
-        <v>465</v>
-      </c>
-      <c r="E29" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F29" s="54">
-        <v>171.9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="64">
-        <v>2</v>
-      </c>
-      <c r="B30" s="64" t="s">
-        <v>607</v>
-      </c>
-      <c r="C30" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D30" s="64" t="s">
-        <v>466</v>
-      </c>
-      <c r="E30" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F30" s="64">
-        <v>130.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="54">
-        <v>2</v>
-      </c>
-      <c r="B31" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D31" s="54" t="s">
-        <v>467</v>
-      </c>
-      <c r="E31" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F31" s="54">
-        <v>38.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="64">
-        <v>2</v>
-      </c>
-      <c r="B32" s="64" t="s">
-        <v>617</v>
-      </c>
-      <c r="C32" s="64" t="s">
-        <v>515</v>
-      </c>
-      <c r="D32" s="64" t="s">
-        <v>556</v>
-      </c>
-      <c r="E32" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F32" s="64">
-        <v>20.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="54">
-        <v>2</v>
-      </c>
-      <c r="B33" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C33" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D33" s="54" t="s">
-        <v>468</v>
-      </c>
-      <c r="E33" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F33" s="54">
-        <v>34.700000000000003</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="64">
-        <v>2</v>
-      </c>
-      <c r="B34" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C34" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D34" s="64" t="s">
-        <v>469</v>
-      </c>
-      <c r="E34" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F34" s="64">
-        <v>168.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="54">
-        <v>2</v>
-      </c>
-      <c r="B35" s="54" t="s">
-        <v>616</v>
-      </c>
-      <c r="C35" s="54" t="s">
-        <v>514</v>
-      </c>
-      <c r="D35" s="54" t="s">
-        <v>469</v>
-      </c>
-      <c r="E35" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F35" s="54" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="64">
-        <v>2</v>
-      </c>
-      <c r="B36" s="64" t="s">
-        <v>607</v>
-      </c>
-      <c r="C36" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D36" s="64" t="s">
-        <v>470</v>
-      </c>
-      <c r="E36" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F36" s="64">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="54">
-        <v>2</v>
-      </c>
-      <c r="B37" s="54" t="s">
-        <v>606</v>
-      </c>
-      <c r="C37" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D37" s="54" t="s">
-        <v>471</v>
-      </c>
-      <c r="E37" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F37" s="54">
-        <v>66.3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="64">
-        <v>2</v>
-      </c>
-      <c r="B38" s="64" t="s">
-        <v>606</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D38" s="64" t="s">
-        <v>472</v>
-      </c>
-      <c r="E38" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F38" s="64">
-        <v>93.1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="54">
-        <v>2</v>
-      </c>
-      <c r="B39" s="54" t="s">
-        <v>607</v>
-      </c>
-      <c r="C39" s="54" t="s">
-        <v>440</v>
-      </c>
-      <c r="D39" s="54" t="s">
-        <v>473</v>
-      </c>
-      <c r="E39" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="F39" s="54">
-        <v>91.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="64">
-        <v>2</v>
-      </c>
-      <c r="B40" s="64" t="s">
-        <v>614</v>
-      </c>
-      <c r="C40" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="D40" s="64" t="s">
-        <v>474</v>
-      </c>
-      <c r="E40" s="64" t="s">
-        <v>595</v>
-      </c>
-      <c r="F40" s="64">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="74">
-        <v>2</v>
-      </c>
-      <c r="B41" s="74" t="s">
-        <v>607</v>
-      </c>
-      <c r="C41" s="74" t="s">
-        <v>440</v>
-      </c>
-      <c r="D41" s="74" t="s">
-        <v>475</v>
-      </c>
-      <c r="E41" s="74" t="s">
-        <v>595</v>
-      </c>
-      <c r="F41" s="74">
-        <v>129.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>